--- a/public/downloads/invoice-template.xlsx
+++ b/public/downloads/invoice-template.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="72">
   <si>
     <t>Invoice template</t>
   </si>
@@ -25,7 +25,7 @@
     <t>What this does</t>
   </si>
   <si>
-    <t>Produces a single, printable invoice that totals itself and calculates VAT.</t>
+    <t>Produces one printable invoice that totals itself and calculates VAT, plus a log of what you have sent.</t>
   </si>
   <si>
     <t/>
@@ -37,28 +37,28 @@
     <t>1. Fill in your own details once on the Settings sheet. They flow onto every invoice.</t>
   </si>
   <si>
-    <t>2. On the Invoice sheet, fill in the client block, the invoice number and the dates.</t>
-  </si>
-  <si>
-    <t>3. Enter the line items. Amount, subtotal, VAT and total all calculate themselves.</t>
-  </si>
-  <si>
-    <t>4. Print to PDF. The page is already set up to fit one sheet of A4 portrait.</t>
+    <t>2. On the Invoice sheet, fill the cream cells: client block, invoice number and date.</t>
+  </si>
+  <si>
+    <t>3. Enter the line items. Amount, subtotal, VAT and total all calculate.</t>
+  </si>
+  <si>
+    <t>4. Print to PDF. The page is already set to fit one sheet of A4 portrait.</t>
   </si>
   <si>
     <t>VAT</t>
   </si>
   <si>
-    <t>The rate comes from the Settings sheet. Set it to 0 if you are not VAT registered, and the VAT line will show zero rather than disappearing — which is the correct thing to show a client.</t>
+    <t>The rate comes from the Settings sheet. Set it to 0 if you are not VAT registered — the line then shows zero rather than disappearing, which is the correct thing to show a client.</t>
   </si>
   <si>
     <t>Keeping a record</t>
   </si>
   <si>
-    <t>Log each invoice on the Invoice log sheet as you send it. The outstanding total at the top tells you what you are owed.</t>
-  </si>
-  <si>
-    <t>Cells with a white background are for you to fill in. Shaded cells hold formulas — changing one replaces the calculation with whatever you typed.</t>
+    <t>Add a row to the Invoice log as you send each one. The outstanding figure at the top totals everything still marked Unpaid.</t>
+  </si>
+  <si>
+    <t>Blue text on a cream background marks a cell you fill in. Black text is calculated — typing over one replaces the formula. Green shading is a heading or a total. This is the standard financial-modelling convention.</t>
   </si>
   <si>
     <t>Your details</t>
@@ -199,7 +199,10 @@
     <t>Invoice log</t>
   </si>
   <si>
-    <t>Outstanding</t>
+    <t>One row per invoice sent</t>
+  </si>
+  <si>
+    <t>OUTSTANDING</t>
   </si>
   <si>
     <t>Client</t>
@@ -237,7 +240,7 @@
     <numFmt numFmtId="164" formatCode="dd mmm yyyy"/>
     <numFmt numFmtId="165" formatCode="&quot;£&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -247,30 +250,30 @@
     </font>
     <font>
       <b/>
-      <color rgb="FF16324F"/>
-      <sz val="16"/>
-      <name val="Calibri"/>
+      <color rgb="FF0A4A3A"/>
+      <sz val="15"/>
+      <name val="Arial"/>
     </font>
     <font>
       <i/>
-      <color rgb="FF5A6B7B"/>
+      <color rgb="FF4A4A48"/>
       <sz val="10"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <color rgb="FF16324F"/>
+      <color rgb="FF0A4A3A"/>
       <sz val="11"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
     </font>
     <font>
-      <color rgb="FF16324F"/>
+      <color rgb="FF141414"/>
       <sz val="10"/>
       <name val="Calibri"/>
     </font>
     <font>
       <i/>
-      <color rgb="FF5A6B7B"/>
+      <color rgb="FF4A4A48"/>
       <sz val="9"/>
       <name val="Calibri"/>
     </font>
@@ -278,28 +281,33 @@
       <b/>
       <color rgb="FFFFFFFF"/>
       <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF0A4A3A"/>
+      <sz val="10"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <b/>
-      <color rgb="FF16324F"/>
+      <color rgb="FF0000FF"/>
       <sz val="10"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <color rgb="FF16324F"/>
-      <sz val="18"/>
-      <name val="Calibri"/>
+      <color rgb="FF0A4A3A"/>
+      <sz val="17"/>
+      <name val="Arial"/>
     </font>
     <font>
       <b/>
-      <color rgb="FF2E7D5B"/>
-      <sz val="18"/>
-      <name val="Calibri"/>
+      <color rgb="FF0F6E56"/>
+      <sz val="17"/>
+      <name val="Arial"/>
     </font>
     <font>
-      <color rgb="FF5A6B7B"/>
+      <color rgb="FF4A4A48"/>
       <sz val="10"/>
       <name val="Calibri"/>
     </font>
@@ -307,26 +315,38 @@
       <b/>
       <color rgb="FFFFFFFF"/>
       <sz val="12"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
     </font>
     <font>
-      <color rgb="FF5A6B7B"/>
+      <b/>
+      <color rgb="FF0A4A3A"/>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <color rgb="FF4A4A48"/>
       <sz val="9"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <color rgb="FF16324F"/>
+      <color rgb="FF141414"/>
       <sz val="9"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <color rgb="FFB4232B"/>
-      <sz val="12"/>
+      <color rgb="FF4A4A48"/>
+      <sz val="9"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <b/>
+      <color rgb="FF7A2020"/>
+      <sz val="14"/>
+      <name val="Arial"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -335,17 +355,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF16324F"/>
+        <fgColor rgb="FFE1F5EE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF4F7F9"/>
+        <fgColor rgb="FF0F6E56"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF2E7D5B"/>
+        <fgColor rgb="FFFFFDF0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAFAF8"/>
       </patternFill>
     </fill>
   </fills>
@@ -359,16 +384,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFD8DEE4"/>
+        <color rgb="FFE4E4E0"/>
       </left>
       <right style="thin">
-        <color rgb="FFD8DEE4"/>
+        <color rgb="FFE4E4E0"/>
       </right>
       <top style="thin">
-        <color rgb="FFD8DEE4"/>
+        <color rgb="FFE4E4E0"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFD8DEE4"/>
+        <color rgb="FFE4E4E0"/>
       </bottom>
       <diagonal/>
     </border>
@@ -376,67 +401,73 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="centerContinuous"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="8" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="8" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="12" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous"/>
-    </xf>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous"/>
-    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="17" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -445,17 +476,22 @@
     <dxf>
       <font>
         <b/>
-        <color rgb="FF2E7D5B"/>
+        <color rgb="FF0A4A3A"/>
       </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE1F5EE"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
         <b/>
-        <color rgb="FFB4232B"/>
+        <color rgb="FF7A2020"/>
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFAD5D3"/>
+          <bgColor rgb="FFF6DEDE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -795,17 +831,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
-    <tabColor rgb="FF5A6B7B"/>
+    <tabColor rgb="FF4A4A48"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:B20"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
-    <col min="2" max="2" width="96" customWidth="1"/>
+    <col min="2" max="2" width="94" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -815,88 +851,89 @@
       <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="2"/>
+      <c r="B3" s="4"/>
     </row>
     <row r="5" ht="22" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="5" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="6" ht="16" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B6" s="5" t="s">
+    <row r="6" ht="30" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B6" s="6" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="7" ht="16" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="5" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="6" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="10" ht="16" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="6" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="6" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="6" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="13" ht="16" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="5" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" ht="28" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B15" s="5" t="s">
+    <row r="15" ht="30" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B15" s="6" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="16" ht="16" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="18" ht="28" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B18" s="5" t="s">
+    <row r="18" ht="30" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B18" s="6" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="20" ht="28" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B20" s="6" t="s">
+    <row r="20" ht="30" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B20" s="7" t="s">
         <v>14</v>
       </c>
     </row>
   </sheetData>
+  <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" fitToWidth="1" fitToHeight="0"/>
   <headerFooter>
-    <oddFooter>&amp;L&amp;"Calibri,Italic"Explore Excel&amp;R&amp;"Calibri,Italic"Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;9Explore Excel&amp;R&amp;9Page &amp;P of &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -904,17 +941,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
-    <tabColor rgb="FF5A6B7B"/>
+    <tabColor rgb="FF4A4A48"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
-    <col min="2" max="2" width="42" customWidth="1"/>
+    <col min="2" max="2" width="44" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>15</v>
       </c>
@@ -924,117 +961,118 @@
       <c r="A2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="2"/>
-    </row>
-    <row r="3" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="7" t="s">
+      <c r="B2" s="4"/>
+    </row>
+    <row r="4" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B4" s="8" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="8" t="s">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B5" s="10" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="10" t="s">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="B6" s="10" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="8" t="s">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B7" s="10" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="10" t="s">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="B8" s="10" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="8" t="s">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B9" s="10" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="10" t="s">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="B9" s="11" t="s">
+      <c r="B10" s="10" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="8" t="s">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="B11" s="10" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="10" t="s">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="B11" s="12">
+      <c r="B12" s="12">
         <v>0.2</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="8" t="s">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="B12" s="9" t="s">
+      <c r="B13" s="10" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="10" t="s">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="B13" s="11" t="s">
+      <c r="B14" s="10" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="8" t="s">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="9" t="s">
+      <c r="B15" s="10" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="10" t="s">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="11">
+      <c r="B16" s="10">
         <v>30</v>
       </c>
     </row>
   </sheetData>
+  <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" fitToWidth="1" fitToHeight="0"/>
   <headerFooter>
-    <oddFooter>&amp;L&amp;"Calibri,Italic"Explore Excel&amp;R&amp;"Calibri,Italic"Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;9Explore Excel&amp;R&amp;9Page &amp;P of &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -1042,21 +1080,21 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
-    <tabColor rgb="FF16324F"/>
+    <tabColor rgb="FF0F6E56"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="38" customWidth="1"/>
+    <col min="1" max="1" width="44" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="3" max="3" width="15" customWidth="1"/>
+    <col min="4" max="4" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="13">
-        <f>Settings!B4</f>
+        <f>Settings!B5</f>
       </c>
       <c r="D1" s="14" t="s">
         <v>40</v>
@@ -1064,7 +1102,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="15">
-        <f>Settings!B5</f>
+        <f>Settings!B6</f>
       </c>
       <c r="C2" s="16" t="s">
         <v>41</v>
@@ -1075,7 +1113,7 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="15">
-        <f>Settings!B6</f>
+        <f>Settings!B7</f>
       </c>
       <c r="C3" s="16" t="s">
         <v>43</v>
@@ -1086,239 +1124,245 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="15">
-        <f>Settings!B7</f>
+        <f>Settings!B8</f>
       </c>
       <c r="C4" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="D4" s="18">
-        <f>D3+Settings!B15</f>
+      <c r="D4" s="19">
+        <f>D3+Settings!$B$16</f>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="15">
-        <f>Settings!B8</f>
+        <f>Settings!B9</f>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" s="19" t="s">
+      <c r="A7" s="20" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" s="9" t="s">
+      <c r="A8" s="21" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" s="9" t="s">
+      <c r="A9" s="21" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" s="9" t="s">
+      <c r="A10" s="21" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" s="9" t="s">
+      <c r="A11" s="21" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="13" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="7" t="s">
+    <row r="13" ht="26" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="D13" s="8" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="9" t="s">
+      <c r="A14" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="B14" s="9">
+      <c r="B14" s="10">
         <v>12</v>
       </c>
-      <c r="C14" s="20">
+      <c r="C14" s="22">
         <v>65</v>
       </c>
-      <c r="D14" s="20">
+      <c r="D14" s="23">
         <f>IF(B14="","",B14*C14)</f>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="11" t="s">
+      <c r="A15" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="B15" s="11">
+      <c r="B15" s="10">
         <v>1</v>
       </c>
-      <c r="C15" s="21">
+      <c r="C15" s="22">
         <v>900</v>
       </c>
-      <c r="D15" s="21">
+      <c r="D15" s="24">
         <f>IF(B15="","",B15*C15)</f>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="9" t="s">
+      <c r="A16" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="B16" s="9">
+      <c r="B16" s="10">
         <v>2</v>
       </c>
-      <c r="C16" s="20">
+      <c r="C16" s="22">
         <v>350</v>
       </c>
-      <c r="D16" s="20">
+      <c r="D16" s="23">
         <f>IF(B16="","",B16*C16)</f>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="11"/>
-      <c r="B17" s="11"/>
-      <c r="C17" s="21"/>
-      <c r="D17" s="21">
+      <c r="A17" s="10"/>
+      <c r="B17" s="10"/>
+      <c r="C17" s="22"/>
+      <c r="D17" s="24">
         <f>IF(B17="","",B17*C17)</f>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="9"/>
-      <c r="B18" s="9"/>
-      <c r="C18" s="20"/>
-      <c r="D18" s="20">
+      <c r="A18" s="10"/>
+      <c r="B18" s="10"/>
+      <c r="C18" s="22"/>
+      <c r="D18" s="23">
         <f>IF(B18="","",B18*C18)</f>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="11"/>
-      <c r="B19" s="11"/>
-      <c r="C19" s="21"/>
-      <c r="D19" s="21">
+      <c r="A19" s="10"/>
+      <c r="B19" s="10"/>
+      <c r="C19" s="22"/>
+      <c r="D19" s="24">
         <f>IF(B19="","",B19*C19)</f>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="9"/>
-      <c r="B20" s="9"/>
-      <c r="C20" s="20"/>
-      <c r="D20" s="20">
+      <c r="A20" s="10"/>
+      <c r="B20" s="10"/>
+      <c r="C20" s="22"/>
+      <c r="D20" s="23">
         <f>IF(B20="","",B20*C20)</f>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="11"/>
-      <c r="B21" s="11"/>
-      <c r="C21" s="21"/>
-      <c r="D21" s="21">
+      <c r="A21" s="10"/>
+      <c r="B21" s="10"/>
+      <c r="C21" s="22"/>
+      <c r="D21" s="24">
         <f>IF(B21="","",B21*C21)</f>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="9"/>
-      <c r="B22" s="9"/>
-      <c r="C22" s="20"/>
-      <c r="D22" s="20">
+      <c r="A22" s="10"/>
+      <c r="B22" s="10"/>
+      <c r="C22" s="22"/>
+      <c r="D22" s="23">
         <f>IF(B22="","",B22*C22)</f>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="11"/>
-      <c r="B23" s="11"/>
-      <c r="C23" s="21"/>
-      <c r="D23" s="21">
+      <c r="A23" s="10"/>
+      <c r="B23" s="10"/>
+      <c r="C23" s="22"/>
+      <c r="D23" s="24">
         <f>IF(B23="","",B23*C23)</f>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="9"/>
-      <c r="B24" s="9"/>
-      <c r="C24" s="20"/>
-      <c r="D24" s="20">
+      <c r="A24" s="10"/>
+      <c r="B24" s="10"/>
+      <c r="C24" s="22"/>
+      <c r="D24" s="23">
         <f>IF(B24="","",B24*C24)</f>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="11"/>
-      <c r="B25" s="11"/>
-      <c r="C25" s="21"/>
-      <c r="D25" s="21">
+      <c r="A25" s="10"/>
+      <c r="B25" s="10"/>
+      <c r="C25" s="22"/>
+      <c r="D25" s="24">
         <f>IF(B25="","",B25*C25)</f>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="9"/>
-      <c r="B26" s="9"/>
-      <c r="C26" s="20"/>
-      <c r="D26" s="20">
+      <c r="A26" s="10"/>
+      <c r="B26" s="10"/>
+      <c r="C26" s="22"/>
+      <c r="D26" s="23">
         <f>IF(B26="","",B26*C26)</f>
       </c>
     </row>
     <row r="27" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C27" s="22" t="s">
+      <c r="C27" s="25" t="s">
         <v>56</v>
       </c>
-      <c r="D27" s="20">
+      <c r="D27" s="23">
         <f>SUM(D14:D26)</f>
       </c>
     </row>
     <row r="28" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C28" s="22" t="s">
+      <c r="C28" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="D28" s="20">
-        <f>ROUND(D27*Settings!$B$11,2)</f>
+      <c r="D28" s="23">
+        <f>ROUND(D27*Settings!$B$12,2)</f>
       </c>
     </row>
     <row r="29" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C29" s="23" t="s">
+      <c r="C29" s="26" t="s">
         <v>57</v>
       </c>
-      <c r="D29" s="24">
+      <c r="D29" s="27">
         <f>D27+D28</f>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A31" s="25" t="s">
+      <c r="A31" s="28" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="26" t="s">
+      <c r="A32" s="29" t="s">
         <v>59</v>
       </c>
-      <c r="B32" s="27">
-        <f>Settings!B12</f>
+      <c r="B32" s="30">
+        <f>Settings!B13</f>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="26" t="s">
+      <c r="A33" s="29" t="s">
         <v>35</v>
       </c>
-      <c r="B33" s="27">
-        <f>Settings!B13</f>
+      <c r="B33" s="30">
+        <f>Settings!B14</f>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" s="26" t="s">
+      <c r="A34" s="29" t="s">
         <v>37</v>
       </c>
-      <c r="B34" s="27">
-        <f>Settings!B14</f>
+      <c r="B34" s="30">
+        <f>Settings!B15</f>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36" s="31">
+        <f>"Payment due within "&amp;Settings!$B$16&amp;" days of the invoice date."</f>
       </c>
     </row>
   </sheetData>
+  <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" fitToWidth="1" fitToHeight="0"/>
   <headerFooter>
-    <oddFooter>&amp;L&amp;"Calibri,Italic"Explore Excel&amp;R&amp;"Calibri,Italic"Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;9Explore Excel&amp;R&amp;9Page &amp;P of &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -1326,18 +1370,19 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
-    <tabColor rgb="FF2E7D5B"/>
+    <tabColor rgb="FF0A4A3A"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F105"/>
+  <dimension ref="A1:F107"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="2" width="30" customWidth="1"/>
-    <col min="3" max="6" width="14" customWidth="1"/>
+    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="2" max="2" width="32" customWidth="1"/>
+    <col min="3" max="5" width="15" customWidth="1"/>
+    <col min="6" max="6" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>60</v>
       </c>
@@ -1348,864 +1393,872 @@
       <c r="F1" s="2"/>
     </row>
     <row r="2" ht="16" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="28" t="s">
+      <c r="A2" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B2" s="29">
-        <f>SUMIFS(E6:E105,F6:F105,"Unpaid")</f>
-      </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-    </row>
-    <row r="5" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="7" t="s">
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" s="32" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="5" ht="24" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" s="33">
+        <f>SUMIFS(E8:E107,F8:F107,"Unpaid")</f>
+      </c>
+    </row>
+    <row r="7" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="C5" s="7" t="s">
+      <c r="B7" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="C7" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="D7" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="E7" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="F5" s="7" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="9" t="s">
+      <c r="F7" s="8" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="34" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="C6" s="30">
+      <c r="B8" s="34" t="s">
+        <v>67</v>
+      </c>
+      <c r="C8" s="35">
         <v>46030</v>
       </c>
-      <c r="D6" s="30">
+      <c r="D8" s="35">
         <v>46060</v>
       </c>
-      <c r="E6" s="20">
+      <c r="E8" s="23">
         <v>2020</v>
       </c>
-      <c r="F6" s="9" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="11" t="s">
+      <c r="F8" s="34" t="s">
         <v>68</v>
       </c>
-      <c r="B7" s="11" t="s">
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="36" t="s">
         <v>69</v>
       </c>
-      <c r="C7" s="31">
+      <c r="B9" s="36" t="s">
+        <v>70</v>
+      </c>
+      <c r="C9" s="37">
         <v>46033</v>
       </c>
-      <c r="D7" s="31">
+      <c r="D9" s="37">
         <v>46063</v>
       </c>
-      <c r="E7" s="21">
+      <c r="E9" s="24">
         <v>780</v>
       </c>
-      <c r="F7" s="11" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="9"/>
-      <c r="B8" s="9"/>
-      <c r="C8" s="30"/>
-      <c r="D8" s="30"/>
-      <c r="E8" s="20"/>
-      <c r="F8" s="9"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="11"/>
-      <c r="B9" s="11"/>
-      <c r="C9" s="31"/>
-      <c r="D9" s="31"/>
-      <c r="E9" s="21"/>
-      <c r="F9" s="11"/>
+      <c r="F9" s="36" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="9"/>
-      <c r="B10" s="9"/>
-      <c r="C10" s="30"/>
-      <c r="D10" s="30"/>
-      <c r="E10" s="20"/>
-      <c r="F10" s="9"/>
+      <c r="A10" s="34"/>
+      <c r="B10" s="34"/>
+      <c r="C10" s="35"/>
+      <c r="D10" s="35"/>
+      <c r="E10" s="23"/>
+      <c r="F10" s="34"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="11"/>
-      <c r="B11" s="11"/>
-      <c r="C11" s="31"/>
-      <c r="D11" s="31"/>
-      <c r="E11" s="21"/>
-      <c r="F11" s="11"/>
+      <c r="A11" s="36"/>
+      <c r="B11" s="36"/>
+      <c r="C11" s="37"/>
+      <c r="D11" s="37"/>
+      <c r="E11" s="24"/>
+      <c r="F11" s="36"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="9"/>
-      <c r="B12" s="9"/>
-      <c r="C12" s="30"/>
-      <c r="D12" s="30"/>
-      <c r="E12" s="20"/>
-      <c r="F12" s="9"/>
+      <c r="A12" s="34"/>
+      <c r="B12" s="34"/>
+      <c r="C12" s="35"/>
+      <c r="D12" s="35"/>
+      <c r="E12" s="23"/>
+      <c r="F12" s="34"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="11"/>
-      <c r="B13" s="11"/>
-      <c r="C13" s="31"/>
-      <c r="D13" s="31"/>
-      <c r="E13" s="21"/>
-      <c r="F13" s="11"/>
+      <c r="A13" s="36"/>
+      <c r="B13" s="36"/>
+      <c r="C13" s="37"/>
+      <c r="D13" s="37"/>
+      <c r="E13" s="24"/>
+      <c r="F13" s="36"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="9"/>
-      <c r="B14" s="9"/>
-      <c r="C14" s="30"/>
-      <c r="D14" s="30"/>
-      <c r="E14" s="20"/>
-      <c r="F14" s="9"/>
+      <c r="A14" s="34"/>
+      <c r="B14" s="34"/>
+      <c r="C14" s="35"/>
+      <c r="D14" s="35"/>
+      <c r="E14" s="23"/>
+      <c r="F14" s="34"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="11"/>
-      <c r="B15" s="11"/>
-      <c r="C15" s="31"/>
-      <c r="D15" s="31"/>
-      <c r="E15" s="21"/>
-      <c r="F15" s="11"/>
+      <c r="A15" s="36"/>
+      <c r="B15" s="36"/>
+      <c r="C15" s="37"/>
+      <c r="D15" s="37"/>
+      <c r="E15" s="24"/>
+      <c r="F15" s="36"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="9"/>
-      <c r="B16" s="9"/>
-      <c r="C16" s="30"/>
-      <c r="D16" s="30"/>
-      <c r="E16" s="20"/>
-      <c r="F16" s="9"/>
+      <c r="A16" s="34"/>
+      <c r="B16" s="34"/>
+      <c r="C16" s="35"/>
+      <c r="D16" s="35"/>
+      <c r="E16" s="23"/>
+      <c r="F16" s="34"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="11"/>
-      <c r="B17" s="11"/>
-      <c r="C17" s="31"/>
-      <c r="D17" s="31"/>
-      <c r="E17" s="21"/>
-      <c r="F17" s="11"/>
+      <c r="A17" s="36"/>
+      <c r="B17" s="36"/>
+      <c r="C17" s="37"/>
+      <c r="D17" s="37"/>
+      <c r="E17" s="24"/>
+      <c r="F17" s="36"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="9"/>
-      <c r="B18" s="9"/>
-      <c r="C18" s="30"/>
-      <c r="D18" s="30"/>
-      <c r="E18" s="20"/>
-      <c r="F18" s="9"/>
+      <c r="A18" s="34"/>
+      <c r="B18" s="34"/>
+      <c r="C18" s="35"/>
+      <c r="D18" s="35"/>
+      <c r="E18" s="23"/>
+      <c r="F18" s="34"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="11"/>
-      <c r="B19" s="11"/>
-      <c r="C19" s="31"/>
-      <c r="D19" s="31"/>
-      <c r="E19" s="21"/>
-      <c r="F19" s="11"/>
+      <c r="A19" s="36"/>
+      <c r="B19" s="36"/>
+      <c r="C19" s="37"/>
+      <c r="D19" s="37"/>
+      <c r="E19" s="24"/>
+      <c r="F19" s="36"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="9"/>
-      <c r="B20" s="9"/>
-      <c r="C20" s="30"/>
-      <c r="D20" s="30"/>
-      <c r="E20" s="20"/>
-      <c r="F20" s="9"/>
+      <c r="A20" s="34"/>
+      <c r="B20" s="34"/>
+      <c r="C20" s="35"/>
+      <c r="D20" s="35"/>
+      <c r="E20" s="23"/>
+      <c r="F20" s="34"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="11"/>
-      <c r="B21" s="11"/>
-      <c r="C21" s="31"/>
-      <c r="D21" s="31"/>
-      <c r="E21" s="21"/>
-      <c r="F21" s="11"/>
+      <c r="A21" s="36"/>
+      <c r="B21" s="36"/>
+      <c r="C21" s="37"/>
+      <c r="D21" s="37"/>
+      <c r="E21" s="24"/>
+      <c r="F21" s="36"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="9"/>
-      <c r="B22" s="9"/>
-      <c r="C22" s="30"/>
-      <c r="D22" s="30"/>
-      <c r="E22" s="20"/>
-      <c r="F22" s="9"/>
+      <c r="A22" s="34"/>
+      <c r="B22" s="34"/>
+      <c r="C22" s="35"/>
+      <c r="D22" s="35"/>
+      <c r="E22" s="23"/>
+      <c r="F22" s="34"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="11"/>
-      <c r="B23" s="11"/>
-      <c r="C23" s="31"/>
-      <c r="D23" s="31"/>
-      <c r="E23" s="21"/>
-      <c r="F23" s="11"/>
+      <c r="A23" s="36"/>
+      <c r="B23" s="36"/>
+      <c r="C23" s="37"/>
+      <c r="D23" s="37"/>
+      <c r="E23" s="24"/>
+      <c r="F23" s="36"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="9"/>
-      <c r="B24" s="9"/>
-      <c r="C24" s="30"/>
-      <c r="D24" s="30"/>
-      <c r="E24" s="20"/>
-      <c r="F24" s="9"/>
+      <c r="A24" s="34"/>
+      <c r="B24" s="34"/>
+      <c r="C24" s="35"/>
+      <c r="D24" s="35"/>
+      <c r="E24" s="23"/>
+      <c r="F24" s="34"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="11"/>
-      <c r="B25" s="11"/>
-      <c r="C25" s="31"/>
-      <c r="D25" s="31"/>
-      <c r="E25" s="21"/>
-      <c r="F25" s="11"/>
+      <c r="A25" s="36"/>
+      <c r="B25" s="36"/>
+      <c r="C25" s="37"/>
+      <c r="D25" s="37"/>
+      <c r="E25" s="24"/>
+      <c r="F25" s="36"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="9"/>
-      <c r="B26" s="9"/>
-      <c r="C26" s="30"/>
-      <c r="D26" s="30"/>
-      <c r="E26" s="20"/>
-      <c r="F26" s="9"/>
+      <c r="A26" s="34"/>
+      <c r="B26" s="34"/>
+      <c r="C26" s="35"/>
+      <c r="D26" s="35"/>
+      <c r="E26" s="23"/>
+      <c r="F26" s="34"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="11"/>
-      <c r="B27" s="11"/>
-      <c r="C27" s="31"/>
-      <c r="D27" s="31"/>
-      <c r="E27" s="21"/>
-      <c r="F27" s="11"/>
+      <c r="A27" s="36"/>
+      <c r="B27" s="36"/>
+      <c r="C27" s="37"/>
+      <c r="D27" s="37"/>
+      <c r="E27" s="24"/>
+      <c r="F27" s="36"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="9"/>
-      <c r="B28" s="9"/>
-      <c r="C28" s="30"/>
-      <c r="D28" s="30"/>
-      <c r="E28" s="20"/>
-      <c r="F28" s="9"/>
+      <c r="A28" s="34"/>
+      <c r="B28" s="34"/>
+      <c r="C28" s="35"/>
+      <c r="D28" s="35"/>
+      <c r="E28" s="23"/>
+      <c r="F28" s="34"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="11"/>
-      <c r="B29" s="11"/>
-      <c r="C29" s="31"/>
-      <c r="D29" s="31"/>
-      <c r="E29" s="21"/>
-      <c r="F29" s="11"/>
+      <c r="A29" s="36"/>
+      <c r="B29" s="36"/>
+      <c r="C29" s="37"/>
+      <c r="D29" s="37"/>
+      <c r="E29" s="24"/>
+      <c r="F29" s="36"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="9"/>
-      <c r="B30" s="9"/>
-      <c r="C30" s="30"/>
-      <c r="D30" s="30"/>
-      <c r="E30" s="20"/>
-      <c r="F30" s="9"/>
+      <c r="A30" s="34"/>
+      <c r="B30" s="34"/>
+      <c r="C30" s="35"/>
+      <c r="D30" s="35"/>
+      <c r="E30" s="23"/>
+      <c r="F30" s="34"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="11"/>
-      <c r="B31" s="11"/>
-      <c r="C31" s="31"/>
-      <c r="D31" s="31"/>
-      <c r="E31" s="21"/>
-      <c r="F31" s="11"/>
+      <c r="A31" s="36"/>
+      <c r="B31" s="36"/>
+      <c r="C31" s="37"/>
+      <c r="D31" s="37"/>
+      <c r="E31" s="24"/>
+      <c r="F31" s="36"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="9"/>
-      <c r="B32" s="9"/>
-      <c r="C32" s="30"/>
-      <c r="D32" s="30"/>
-      <c r="E32" s="20"/>
-      <c r="F32" s="9"/>
+      <c r="A32" s="34"/>
+      <c r="B32" s="34"/>
+      <c r="C32" s="35"/>
+      <c r="D32" s="35"/>
+      <c r="E32" s="23"/>
+      <c r="F32" s="34"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="11"/>
-      <c r="B33" s="11"/>
-      <c r="C33" s="31"/>
-      <c r="D33" s="31"/>
-      <c r="E33" s="21"/>
-      <c r="F33" s="11"/>
+      <c r="A33" s="36"/>
+      <c r="B33" s="36"/>
+      <c r="C33" s="37"/>
+      <c r="D33" s="37"/>
+      <c r="E33" s="24"/>
+      <c r="F33" s="36"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="9"/>
-      <c r="B34" s="9"/>
-      <c r="C34" s="30"/>
-      <c r="D34" s="30"/>
-      <c r="E34" s="20"/>
-      <c r="F34" s="9"/>
+      <c r="A34" s="34"/>
+      <c r="B34" s="34"/>
+      <c r="C34" s="35"/>
+      <c r="D34" s="35"/>
+      <c r="E34" s="23"/>
+      <c r="F34" s="34"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="11"/>
-      <c r="B35" s="11"/>
-      <c r="C35" s="31"/>
-      <c r="D35" s="31"/>
-      <c r="E35" s="21"/>
-      <c r="F35" s="11"/>
+      <c r="A35" s="36"/>
+      <c r="B35" s="36"/>
+      <c r="C35" s="37"/>
+      <c r="D35" s="37"/>
+      <c r="E35" s="24"/>
+      <c r="F35" s="36"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="9"/>
-      <c r="B36" s="9"/>
-      <c r="C36" s="30"/>
-      <c r="D36" s="30"/>
-      <c r="E36" s="20"/>
-      <c r="F36" s="9"/>
+      <c r="A36" s="34"/>
+      <c r="B36" s="34"/>
+      <c r="C36" s="35"/>
+      <c r="D36" s="35"/>
+      <c r="E36" s="23"/>
+      <c r="F36" s="34"/>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="11"/>
-      <c r="B37" s="11"/>
-      <c r="C37" s="31"/>
-      <c r="D37" s="31"/>
-      <c r="E37" s="21"/>
-      <c r="F37" s="11"/>
+      <c r="A37" s="36"/>
+      <c r="B37" s="36"/>
+      <c r="C37" s="37"/>
+      <c r="D37" s="37"/>
+      <c r="E37" s="24"/>
+      <c r="F37" s="36"/>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="9"/>
-      <c r="B38" s="9"/>
-      <c r="C38" s="30"/>
-      <c r="D38" s="30"/>
-      <c r="E38" s="20"/>
-      <c r="F38" s="9"/>
+      <c r="A38" s="34"/>
+      <c r="B38" s="34"/>
+      <c r="C38" s="35"/>
+      <c r="D38" s="35"/>
+      <c r="E38" s="23"/>
+      <c r="F38" s="34"/>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="11"/>
-      <c r="B39" s="11"/>
-      <c r="C39" s="31"/>
-      <c r="D39" s="31"/>
-      <c r="E39" s="21"/>
-      <c r="F39" s="11"/>
+      <c r="A39" s="36"/>
+      <c r="B39" s="36"/>
+      <c r="C39" s="37"/>
+      <c r="D39" s="37"/>
+      <c r="E39" s="24"/>
+      <c r="F39" s="36"/>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="9"/>
-      <c r="B40" s="9"/>
-      <c r="C40" s="30"/>
-      <c r="D40" s="30"/>
-      <c r="E40" s="20"/>
-      <c r="F40" s="9"/>
+      <c r="A40" s="34"/>
+      <c r="B40" s="34"/>
+      <c r="C40" s="35"/>
+      <c r="D40" s="35"/>
+      <c r="E40" s="23"/>
+      <c r="F40" s="34"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="11"/>
-      <c r="B41" s="11"/>
-      <c r="C41" s="31"/>
-      <c r="D41" s="31"/>
-      <c r="E41" s="21"/>
-      <c r="F41" s="11"/>
+      <c r="A41" s="36"/>
+      <c r="B41" s="36"/>
+      <c r="C41" s="37"/>
+      <c r="D41" s="37"/>
+      <c r="E41" s="24"/>
+      <c r="F41" s="36"/>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="9"/>
-      <c r="B42" s="9"/>
-      <c r="C42" s="30"/>
-      <c r="D42" s="30"/>
-      <c r="E42" s="20"/>
-      <c r="F42" s="9"/>
+      <c r="A42" s="34"/>
+      <c r="B42" s="34"/>
+      <c r="C42" s="35"/>
+      <c r="D42" s="35"/>
+      <c r="E42" s="23"/>
+      <c r="F42" s="34"/>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="11"/>
-      <c r="B43" s="11"/>
-      <c r="C43" s="31"/>
-      <c r="D43" s="31"/>
-      <c r="E43" s="21"/>
-      <c r="F43" s="11"/>
+      <c r="A43" s="36"/>
+      <c r="B43" s="36"/>
+      <c r="C43" s="37"/>
+      <c r="D43" s="37"/>
+      <c r="E43" s="24"/>
+      <c r="F43" s="36"/>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="9"/>
-      <c r="B44" s="9"/>
-      <c r="C44" s="30"/>
-      <c r="D44" s="30"/>
-      <c r="E44" s="20"/>
-      <c r="F44" s="9"/>
+      <c r="A44" s="34"/>
+      <c r="B44" s="34"/>
+      <c r="C44" s="35"/>
+      <c r="D44" s="35"/>
+      <c r="E44" s="23"/>
+      <c r="F44" s="34"/>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="11"/>
-      <c r="B45" s="11"/>
-      <c r="C45" s="31"/>
-      <c r="D45" s="31"/>
-      <c r="E45" s="21"/>
-      <c r="F45" s="11"/>
+      <c r="A45" s="36"/>
+      <c r="B45" s="36"/>
+      <c r="C45" s="37"/>
+      <c r="D45" s="37"/>
+      <c r="E45" s="24"/>
+      <c r="F45" s="36"/>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="9"/>
-      <c r="B46" s="9"/>
-      <c r="C46" s="30"/>
-      <c r="D46" s="30"/>
-      <c r="E46" s="20"/>
-      <c r="F46" s="9"/>
+      <c r="A46" s="34"/>
+      <c r="B46" s="34"/>
+      <c r="C46" s="35"/>
+      <c r="D46" s="35"/>
+      <c r="E46" s="23"/>
+      <c r="F46" s="34"/>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="11"/>
-      <c r="B47" s="11"/>
-      <c r="C47" s="31"/>
-      <c r="D47" s="31"/>
-      <c r="E47" s="21"/>
-      <c r="F47" s="11"/>
+      <c r="A47" s="36"/>
+      <c r="B47" s="36"/>
+      <c r="C47" s="37"/>
+      <c r="D47" s="37"/>
+      <c r="E47" s="24"/>
+      <c r="F47" s="36"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" s="9"/>
-      <c r="B48" s="9"/>
-      <c r="C48" s="30"/>
-      <c r="D48" s="30"/>
-      <c r="E48" s="20"/>
-      <c r="F48" s="9"/>
+      <c r="A48" s="34"/>
+      <c r="B48" s="34"/>
+      <c r="C48" s="35"/>
+      <c r="D48" s="35"/>
+      <c r="E48" s="23"/>
+      <c r="F48" s="34"/>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" s="11"/>
-      <c r="B49" s="11"/>
-      <c r="C49" s="31"/>
-      <c r="D49" s="31"/>
-      <c r="E49" s="21"/>
-      <c r="F49" s="11"/>
+      <c r="A49" s="36"/>
+      <c r="B49" s="36"/>
+      <c r="C49" s="37"/>
+      <c r="D49" s="37"/>
+      <c r="E49" s="24"/>
+      <c r="F49" s="36"/>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="9"/>
-      <c r="B50" s="9"/>
-      <c r="C50" s="30"/>
-      <c r="D50" s="30"/>
-      <c r="E50" s="20"/>
-      <c r="F50" s="9"/>
+      <c r="A50" s="34"/>
+      <c r="B50" s="34"/>
+      <c r="C50" s="35"/>
+      <c r="D50" s="35"/>
+      <c r="E50" s="23"/>
+      <c r="F50" s="34"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" s="11"/>
-      <c r="B51" s="11"/>
-      <c r="C51" s="31"/>
-      <c r="D51" s="31"/>
-      <c r="E51" s="21"/>
-      <c r="F51" s="11"/>
+      <c r="A51" s="36"/>
+      <c r="B51" s="36"/>
+      <c r="C51" s="37"/>
+      <c r="D51" s="37"/>
+      <c r="E51" s="24"/>
+      <c r="F51" s="36"/>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52" s="9"/>
-      <c r="B52" s="9"/>
-      <c r="C52" s="30"/>
-      <c r="D52" s="30"/>
-      <c r="E52" s="20"/>
-      <c r="F52" s="9"/>
+      <c r="A52" s="34"/>
+      <c r="B52" s="34"/>
+      <c r="C52" s="35"/>
+      <c r="D52" s="35"/>
+      <c r="E52" s="23"/>
+      <c r="F52" s="34"/>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53" s="11"/>
-      <c r="B53" s="11"/>
-      <c r="C53" s="31"/>
-      <c r="D53" s="31"/>
-      <c r="E53" s="21"/>
-      <c r="F53" s="11"/>
+      <c r="A53" s="36"/>
+      <c r="B53" s="36"/>
+      <c r="C53" s="37"/>
+      <c r="D53" s="37"/>
+      <c r="E53" s="24"/>
+      <c r="F53" s="36"/>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" s="9"/>
-      <c r="B54" s="9"/>
-      <c r="C54" s="30"/>
-      <c r="D54" s="30"/>
-      <c r="E54" s="20"/>
-      <c r="F54" s="9"/>
+      <c r="A54" s="34"/>
+      <c r="B54" s="34"/>
+      <c r="C54" s="35"/>
+      <c r="D54" s="35"/>
+      <c r="E54" s="23"/>
+      <c r="F54" s="34"/>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55" s="11"/>
-      <c r="B55" s="11"/>
-      <c r="C55" s="31"/>
-      <c r="D55" s="31"/>
-      <c r="E55" s="21"/>
-      <c r="F55" s="11"/>
+      <c r="A55" s="36"/>
+      <c r="B55" s="36"/>
+      <c r="C55" s="37"/>
+      <c r="D55" s="37"/>
+      <c r="E55" s="24"/>
+      <c r="F55" s="36"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" s="9"/>
-      <c r="B56" s="9"/>
-      <c r="C56" s="30"/>
-      <c r="D56" s="30"/>
-      <c r="E56" s="20"/>
-      <c r="F56" s="9"/>
+      <c r="A56" s="34"/>
+      <c r="B56" s="34"/>
+      <c r="C56" s="35"/>
+      <c r="D56" s="35"/>
+      <c r="E56" s="23"/>
+      <c r="F56" s="34"/>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A57" s="11"/>
-      <c r="B57" s="11"/>
-      <c r="C57" s="31"/>
-      <c r="D57" s="31"/>
-      <c r="E57" s="21"/>
-      <c r="F57" s="11"/>
+      <c r="A57" s="36"/>
+      <c r="B57" s="36"/>
+      <c r="C57" s="37"/>
+      <c r="D57" s="37"/>
+      <c r="E57" s="24"/>
+      <c r="F57" s="36"/>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A58" s="9"/>
-      <c r="B58" s="9"/>
-      <c r="C58" s="30"/>
-      <c r="D58" s="30"/>
-      <c r="E58" s="20"/>
-      <c r="F58" s="9"/>
+      <c r="A58" s="34"/>
+      <c r="B58" s="34"/>
+      <c r="C58" s="35"/>
+      <c r="D58" s="35"/>
+      <c r="E58" s="23"/>
+      <c r="F58" s="34"/>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A59" s="11"/>
-      <c r="B59" s="11"/>
-      <c r="C59" s="31"/>
-      <c r="D59" s="31"/>
-      <c r="E59" s="21"/>
-      <c r="F59" s="11"/>
+      <c r="A59" s="36"/>
+      <c r="B59" s="36"/>
+      <c r="C59" s="37"/>
+      <c r="D59" s="37"/>
+      <c r="E59" s="24"/>
+      <c r="F59" s="36"/>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="9"/>
-      <c r="B60" s="9"/>
-      <c r="C60" s="30"/>
-      <c r="D60" s="30"/>
-      <c r="E60" s="20"/>
-      <c r="F60" s="9"/>
+      <c r="A60" s="34"/>
+      <c r="B60" s="34"/>
+      <c r="C60" s="35"/>
+      <c r="D60" s="35"/>
+      <c r="E60" s="23"/>
+      <c r="F60" s="34"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="11"/>
-      <c r="B61" s="11"/>
-      <c r="C61" s="31"/>
-      <c r="D61" s="31"/>
-      <c r="E61" s="21"/>
-      <c r="F61" s="11"/>
+      <c r="A61" s="36"/>
+      <c r="B61" s="36"/>
+      <c r="C61" s="37"/>
+      <c r="D61" s="37"/>
+      <c r="E61" s="24"/>
+      <c r="F61" s="36"/>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="9"/>
-      <c r="B62" s="9"/>
-      <c r="C62" s="30"/>
-      <c r="D62" s="30"/>
-      <c r="E62" s="20"/>
-      <c r="F62" s="9"/>
+      <c r="A62" s="34"/>
+      <c r="B62" s="34"/>
+      <c r="C62" s="35"/>
+      <c r="D62" s="35"/>
+      <c r="E62" s="23"/>
+      <c r="F62" s="34"/>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A63" s="11"/>
-      <c r="B63" s="11"/>
-      <c r="C63" s="31"/>
-      <c r="D63" s="31"/>
-      <c r="E63" s="21"/>
-      <c r="F63" s="11"/>
+      <c r="A63" s="36"/>
+      <c r="B63" s="36"/>
+      <c r="C63" s="37"/>
+      <c r="D63" s="37"/>
+      <c r="E63" s="24"/>
+      <c r="F63" s="36"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A64" s="9"/>
-      <c r="B64" s="9"/>
-      <c r="C64" s="30"/>
-      <c r="D64" s="30"/>
-      <c r="E64" s="20"/>
-      <c r="F64" s="9"/>
+      <c r="A64" s="34"/>
+      <c r="B64" s="34"/>
+      <c r="C64" s="35"/>
+      <c r="D64" s="35"/>
+      <c r="E64" s="23"/>
+      <c r="F64" s="34"/>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A65" s="11"/>
-      <c r="B65" s="11"/>
-      <c r="C65" s="31"/>
-      <c r="D65" s="31"/>
-      <c r="E65" s="21"/>
-      <c r="F65" s="11"/>
+      <c r="A65" s="36"/>
+      <c r="B65" s="36"/>
+      <c r="C65" s="37"/>
+      <c r="D65" s="37"/>
+      <c r="E65" s="24"/>
+      <c r="F65" s="36"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A66" s="9"/>
-      <c r="B66" s="9"/>
-      <c r="C66" s="30"/>
-      <c r="D66" s="30"/>
-      <c r="E66" s="20"/>
-      <c r="F66" s="9"/>
+      <c r="A66" s="34"/>
+      <c r="B66" s="34"/>
+      <c r="C66" s="35"/>
+      <c r="D66" s="35"/>
+      <c r="E66" s="23"/>
+      <c r="F66" s="34"/>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A67" s="11"/>
-      <c r="B67" s="11"/>
-      <c r="C67" s="31"/>
-      <c r="D67" s="31"/>
-      <c r="E67" s="21"/>
-      <c r="F67" s="11"/>
+      <c r="A67" s="36"/>
+      <c r="B67" s="36"/>
+      <c r="C67" s="37"/>
+      <c r="D67" s="37"/>
+      <c r="E67" s="24"/>
+      <c r="F67" s="36"/>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A68" s="9"/>
-      <c r="B68" s="9"/>
-      <c r="C68" s="30"/>
-      <c r="D68" s="30"/>
-      <c r="E68" s="20"/>
-      <c r="F68" s="9"/>
+      <c r="A68" s="34"/>
+      <c r="B68" s="34"/>
+      <c r="C68" s="35"/>
+      <c r="D68" s="35"/>
+      <c r="E68" s="23"/>
+      <c r="F68" s="34"/>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A69" s="11"/>
-      <c r="B69" s="11"/>
-      <c r="C69" s="31"/>
-      <c r="D69" s="31"/>
-      <c r="E69" s="21"/>
-      <c r="F69" s="11"/>
+      <c r="A69" s="36"/>
+      <c r="B69" s="36"/>
+      <c r="C69" s="37"/>
+      <c r="D69" s="37"/>
+      <c r="E69" s="24"/>
+      <c r="F69" s="36"/>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A70" s="9"/>
-      <c r="B70" s="9"/>
-      <c r="C70" s="30"/>
-      <c r="D70" s="30"/>
-      <c r="E70" s="20"/>
-      <c r="F70" s="9"/>
+      <c r="A70" s="34"/>
+      <c r="B70" s="34"/>
+      <c r="C70" s="35"/>
+      <c r="D70" s="35"/>
+      <c r="E70" s="23"/>
+      <c r="F70" s="34"/>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A71" s="11"/>
-      <c r="B71" s="11"/>
-      <c r="C71" s="31"/>
-      <c r="D71" s="31"/>
-      <c r="E71" s="21"/>
-      <c r="F71" s="11"/>
+      <c r="A71" s="36"/>
+      <c r="B71" s="36"/>
+      <c r="C71" s="37"/>
+      <c r="D71" s="37"/>
+      <c r="E71" s="24"/>
+      <c r="F71" s="36"/>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A72" s="9"/>
-      <c r="B72" s="9"/>
-      <c r="C72" s="30"/>
-      <c r="D72" s="30"/>
-      <c r="E72" s="20"/>
-      <c r="F72" s="9"/>
+      <c r="A72" s="34"/>
+      <c r="B72" s="34"/>
+      <c r="C72" s="35"/>
+      <c r="D72" s="35"/>
+      <c r="E72" s="23"/>
+      <c r="F72" s="34"/>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A73" s="11"/>
-      <c r="B73" s="11"/>
-      <c r="C73" s="31"/>
-      <c r="D73" s="31"/>
-      <c r="E73" s="21"/>
-      <c r="F73" s="11"/>
+      <c r="A73" s="36"/>
+      <c r="B73" s="36"/>
+      <c r="C73" s="37"/>
+      <c r="D73" s="37"/>
+      <c r="E73" s="24"/>
+      <c r="F73" s="36"/>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A74" s="9"/>
-      <c r="B74" s="9"/>
-      <c r="C74" s="30"/>
-      <c r="D74" s="30"/>
-      <c r="E74" s="20"/>
-      <c r="F74" s="9"/>
+      <c r="A74" s="34"/>
+      <c r="B74" s="34"/>
+      <c r="C74" s="35"/>
+      <c r="D74" s="35"/>
+      <c r="E74" s="23"/>
+      <c r="F74" s="34"/>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A75" s="11"/>
-      <c r="B75" s="11"/>
-      <c r="C75" s="31"/>
-      <c r="D75" s="31"/>
-      <c r="E75" s="21"/>
-      <c r="F75" s="11"/>
+      <c r="A75" s="36"/>
+      <c r="B75" s="36"/>
+      <c r="C75" s="37"/>
+      <c r="D75" s="37"/>
+      <c r="E75" s="24"/>
+      <c r="F75" s="36"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A76" s="9"/>
-      <c r="B76" s="9"/>
-      <c r="C76" s="30"/>
-      <c r="D76" s="30"/>
-      <c r="E76" s="20"/>
-      <c r="F76" s="9"/>
+      <c r="A76" s="34"/>
+      <c r="B76" s="34"/>
+      <c r="C76" s="35"/>
+      <c r="D76" s="35"/>
+      <c r="E76" s="23"/>
+      <c r="F76" s="34"/>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A77" s="11"/>
-      <c r="B77" s="11"/>
-      <c r="C77" s="31"/>
-      <c r="D77" s="31"/>
-      <c r="E77" s="21"/>
-      <c r="F77" s="11"/>
+      <c r="A77" s="36"/>
+      <c r="B77" s="36"/>
+      <c r="C77" s="37"/>
+      <c r="D77" s="37"/>
+      <c r="E77" s="24"/>
+      <c r="F77" s="36"/>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A78" s="9"/>
-      <c r="B78" s="9"/>
-      <c r="C78" s="30"/>
-      <c r="D78" s="30"/>
-      <c r="E78" s="20"/>
-      <c r="F78" s="9"/>
+      <c r="A78" s="34"/>
+      <c r="B78" s="34"/>
+      <c r="C78" s="35"/>
+      <c r="D78" s="35"/>
+      <c r="E78" s="23"/>
+      <c r="F78" s="34"/>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A79" s="11"/>
-      <c r="B79" s="11"/>
-      <c r="C79" s="31"/>
-      <c r="D79" s="31"/>
-      <c r="E79" s="21"/>
-      <c r="F79" s="11"/>
+      <c r="A79" s="36"/>
+      <c r="B79" s="36"/>
+      <c r="C79" s="37"/>
+      <c r="D79" s="37"/>
+      <c r="E79" s="24"/>
+      <c r="F79" s="36"/>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A80" s="9"/>
-      <c r="B80" s="9"/>
-      <c r="C80" s="30"/>
-      <c r="D80" s="30"/>
-      <c r="E80" s="20"/>
-      <c r="F80" s="9"/>
+      <c r="A80" s="34"/>
+      <c r="B80" s="34"/>
+      <c r="C80" s="35"/>
+      <c r="D80" s="35"/>
+      <c r="E80" s="23"/>
+      <c r="F80" s="34"/>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A81" s="11"/>
-      <c r="B81" s="11"/>
-      <c r="C81" s="31"/>
-      <c r="D81" s="31"/>
-      <c r="E81" s="21"/>
-      <c r="F81" s="11"/>
+      <c r="A81" s="36"/>
+      <c r="B81" s="36"/>
+      <c r="C81" s="37"/>
+      <c r="D81" s="37"/>
+      <c r="E81" s="24"/>
+      <c r="F81" s="36"/>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A82" s="9"/>
-      <c r="B82" s="9"/>
-      <c r="C82" s="30"/>
-      <c r="D82" s="30"/>
-      <c r="E82" s="20"/>
-      <c r="F82" s="9"/>
+      <c r="A82" s="34"/>
+      <c r="B82" s="34"/>
+      <c r="C82" s="35"/>
+      <c r="D82" s="35"/>
+      <c r="E82" s="23"/>
+      <c r="F82" s="34"/>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A83" s="11"/>
-      <c r="B83" s="11"/>
-      <c r="C83" s="31"/>
-      <c r="D83" s="31"/>
-      <c r="E83" s="21"/>
-      <c r="F83" s="11"/>
+      <c r="A83" s="36"/>
+      <c r="B83" s="36"/>
+      <c r="C83" s="37"/>
+      <c r="D83" s="37"/>
+      <c r="E83" s="24"/>
+      <c r="F83" s="36"/>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A84" s="9"/>
-      <c r="B84" s="9"/>
-      <c r="C84" s="30"/>
-      <c r="D84" s="30"/>
-      <c r="E84" s="20"/>
-      <c r="F84" s="9"/>
+      <c r="A84" s="34"/>
+      <c r="B84" s="34"/>
+      <c r="C84" s="35"/>
+      <c r="D84" s="35"/>
+      <c r="E84" s="23"/>
+      <c r="F84" s="34"/>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A85" s="11"/>
-      <c r="B85" s="11"/>
-      <c r="C85" s="31"/>
-      <c r="D85" s="31"/>
-      <c r="E85" s="21"/>
-      <c r="F85" s="11"/>
+      <c r="A85" s="36"/>
+      <c r="B85" s="36"/>
+      <c r="C85" s="37"/>
+      <c r="D85" s="37"/>
+      <c r="E85" s="24"/>
+      <c r="F85" s="36"/>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A86" s="9"/>
-      <c r="B86" s="9"/>
-      <c r="C86" s="30"/>
-      <c r="D86" s="30"/>
-      <c r="E86" s="20"/>
-      <c r="F86" s="9"/>
+      <c r="A86" s="34"/>
+      <c r="B86" s="34"/>
+      <c r="C86" s="35"/>
+      <c r="D86" s="35"/>
+      <c r="E86" s="23"/>
+      <c r="F86" s="34"/>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A87" s="11"/>
-      <c r="B87" s="11"/>
-      <c r="C87" s="31"/>
-      <c r="D87" s="31"/>
-      <c r="E87" s="21"/>
-      <c r="F87" s="11"/>
+      <c r="A87" s="36"/>
+      <c r="B87" s="36"/>
+      <c r="C87" s="37"/>
+      <c r="D87" s="37"/>
+      <c r="E87" s="24"/>
+      <c r="F87" s="36"/>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A88" s="9"/>
-      <c r="B88" s="9"/>
-      <c r="C88" s="30"/>
-      <c r="D88" s="30"/>
-      <c r="E88" s="20"/>
-      <c r="F88" s="9"/>
+      <c r="A88" s="34"/>
+      <c r="B88" s="34"/>
+      <c r="C88" s="35"/>
+      <c r="D88" s="35"/>
+      <c r="E88" s="23"/>
+      <c r="F88" s="34"/>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A89" s="11"/>
-      <c r="B89" s="11"/>
-      <c r="C89" s="31"/>
-      <c r="D89" s="31"/>
-      <c r="E89" s="21"/>
-      <c r="F89" s="11"/>
+      <c r="A89" s="36"/>
+      <c r="B89" s="36"/>
+      <c r="C89" s="37"/>
+      <c r="D89" s="37"/>
+      <c r="E89" s="24"/>
+      <c r="F89" s="36"/>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A90" s="9"/>
-      <c r="B90" s="9"/>
-      <c r="C90" s="30"/>
-      <c r="D90" s="30"/>
-      <c r="E90" s="20"/>
-      <c r="F90" s="9"/>
+      <c r="A90" s="34"/>
+      <c r="B90" s="34"/>
+      <c r="C90" s="35"/>
+      <c r="D90" s="35"/>
+      <c r="E90" s="23"/>
+      <c r="F90" s="34"/>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A91" s="11"/>
-      <c r="B91" s="11"/>
-      <c r="C91" s="31"/>
-      <c r="D91" s="31"/>
-      <c r="E91" s="21"/>
-      <c r="F91" s="11"/>
+      <c r="A91" s="36"/>
+      <c r="B91" s="36"/>
+      <c r="C91" s="37"/>
+      <c r="D91" s="37"/>
+      <c r="E91" s="24"/>
+      <c r="F91" s="36"/>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A92" s="9"/>
-      <c r="B92" s="9"/>
-      <c r="C92" s="30"/>
-      <c r="D92" s="30"/>
-      <c r="E92" s="20"/>
-      <c r="F92" s="9"/>
+      <c r="A92" s="34"/>
+      <c r="B92" s="34"/>
+      <c r="C92" s="35"/>
+      <c r="D92" s="35"/>
+      <c r="E92" s="23"/>
+      <c r="F92" s="34"/>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A93" s="11"/>
-      <c r="B93" s="11"/>
-      <c r="C93" s="31"/>
-      <c r="D93" s="31"/>
-      <c r="E93" s="21"/>
-      <c r="F93" s="11"/>
+      <c r="A93" s="36"/>
+      <c r="B93" s="36"/>
+      <c r="C93" s="37"/>
+      <c r="D93" s="37"/>
+      <c r="E93" s="24"/>
+      <c r="F93" s="36"/>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A94" s="9"/>
-      <c r="B94" s="9"/>
-      <c r="C94" s="30"/>
-      <c r="D94" s="30"/>
-      <c r="E94" s="20"/>
-      <c r="F94" s="9"/>
+      <c r="A94" s="34"/>
+      <c r="B94" s="34"/>
+      <c r="C94" s="35"/>
+      <c r="D94" s="35"/>
+      <c r="E94" s="23"/>
+      <c r="F94" s="34"/>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A95" s="11"/>
-      <c r="B95" s="11"/>
-      <c r="C95" s="31"/>
-      <c r="D95" s="31"/>
-      <c r="E95" s="21"/>
-      <c r="F95" s="11"/>
+      <c r="A95" s="36"/>
+      <c r="B95" s="36"/>
+      <c r="C95" s="37"/>
+      <c r="D95" s="37"/>
+      <c r="E95" s="24"/>
+      <c r="F95" s="36"/>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A96" s="9"/>
-      <c r="B96" s="9"/>
-      <c r="C96" s="30"/>
-      <c r="D96" s="30"/>
-      <c r="E96" s="20"/>
-      <c r="F96" s="9"/>
+      <c r="A96" s="34"/>
+      <c r="B96" s="34"/>
+      <c r="C96" s="35"/>
+      <c r="D96" s="35"/>
+      <c r="E96" s="23"/>
+      <c r="F96" s="34"/>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A97" s="11"/>
-      <c r="B97" s="11"/>
-      <c r="C97" s="31"/>
-      <c r="D97" s="31"/>
-      <c r="E97" s="21"/>
-      <c r="F97" s="11"/>
+      <c r="A97" s="36"/>
+      <c r="B97" s="36"/>
+      <c r="C97" s="37"/>
+      <c r="D97" s="37"/>
+      <c r="E97" s="24"/>
+      <c r="F97" s="36"/>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A98" s="9"/>
-      <c r="B98" s="9"/>
-      <c r="C98" s="30"/>
-      <c r="D98" s="30"/>
-      <c r="E98" s="20"/>
-      <c r="F98" s="9"/>
+      <c r="A98" s="34"/>
+      <c r="B98" s="34"/>
+      <c r="C98" s="35"/>
+      <c r="D98" s="35"/>
+      <c r="E98" s="23"/>
+      <c r="F98" s="34"/>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A99" s="11"/>
-      <c r="B99" s="11"/>
-      <c r="C99" s="31"/>
-      <c r="D99" s="31"/>
-      <c r="E99" s="21"/>
-      <c r="F99" s="11"/>
+      <c r="A99" s="36"/>
+      <c r="B99" s="36"/>
+      <c r="C99" s="37"/>
+      <c r="D99" s="37"/>
+      <c r="E99" s="24"/>
+      <c r="F99" s="36"/>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A100" s="9"/>
-      <c r="B100" s="9"/>
-      <c r="C100" s="30"/>
-      <c r="D100" s="30"/>
-      <c r="E100" s="20"/>
-      <c r="F100" s="9"/>
+      <c r="A100" s="34"/>
+      <c r="B100" s="34"/>
+      <c r="C100" s="35"/>
+      <c r="D100" s="35"/>
+      <c r="E100" s="23"/>
+      <c r="F100" s="34"/>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A101" s="11"/>
-      <c r="B101" s="11"/>
-      <c r="C101" s="31"/>
-      <c r="D101" s="31"/>
-      <c r="E101" s="21"/>
-      <c r="F101" s="11"/>
+      <c r="A101" s="36"/>
+      <c r="B101" s="36"/>
+      <c r="C101" s="37"/>
+      <c r="D101" s="37"/>
+      <c r="E101" s="24"/>
+      <c r="F101" s="36"/>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A102" s="9"/>
-      <c r="B102" s="9"/>
-      <c r="C102" s="30"/>
-      <c r="D102" s="30"/>
-      <c r="E102" s="20"/>
-      <c r="F102" s="9"/>
+      <c r="A102" s="34"/>
+      <c r="B102" s="34"/>
+      <c r="C102" s="35"/>
+      <c r="D102" s="35"/>
+      <c r="E102" s="23"/>
+      <c r="F102" s="34"/>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A103" s="11"/>
-      <c r="B103" s="11"/>
-      <c r="C103" s="31"/>
-      <c r="D103" s="31"/>
-      <c r="E103" s="21"/>
-      <c r="F103" s="11"/>
+      <c r="A103" s="36"/>
+      <c r="B103" s="36"/>
+      <c r="C103" s="37"/>
+      <c r="D103" s="37"/>
+      <c r="E103" s="24"/>
+      <c r="F103" s="36"/>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A104" s="9"/>
-      <c r="B104" s="9"/>
-      <c r="C104" s="30"/>
-      <c r="D104" s="30"/>
-      <c r="E104" s="20"/>
-      <c r="F104" s="9"/>
+      <c r="A104" s="34"/>
+      <c r="B104" s="34"/>
+      <c r="C104" s="35"/>
+      <c r="D104" s="35"/>
+      <c r="E104" s="23"/>
+      <c r="F104" s="34"/>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A105" s="11"/>
-      <c r="B105" s="11"/>
-      <c r="C105" s="31"/>
-      <c r="D105" s="31"/>
-      <c r="E105" s="21"/>
-      <c r="F105" s="11"/>
+      <c r="A105" s="36"/>
+      <c r="B105" s="36"/>
+      <c r="C105" s="37"/>
+      <c r="D105" s="37"/>
+      <c r="E105" s="24"/>
+      <c r="F105" s="36"/>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A106" s="34"/>
+      <c r="B106" s="34"/>
+      <c r="C106" s="35"/>
+      <c r="D106" s="35"/>
+      <c r="E106" s="23"/>
+      <c r="F106" s="34"/>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A107" s="36"/>
+      <c r="B107" s="36"/>
+      <c r="C107" s="37"/>
+      <c r="D107" s="37"/>
+      <c r="E107" s="24"/>
+      <c r="F107" s="36"/>
     </row>
   </sheetData>
-  <autoFilter ref="A5:F5"/>
-  <conditionalFormatting sqref="F6:F105">
+  <autoFilter ref="A7:F7"/>
+  <conditionalFormatting sqref="F8:F107">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"Paid"</formula>
     </cfRule>
@@ -2213,18 +2266,16 @@
       <formula>"Overdue"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" sqref="F10:F105">
-      <formula1>"Unpaid,Paid,Overdue,Written off"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="F6:F105">
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Unknown status" error="Choose Unpaid, Paid, Overdue or Written off." sqref="F8:F107">
       <formula1>"Unpaid,Paid,Overdue,Written off"</formula1>
     </dataValidation>
   </dataValidations>
+  <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" fitToWidth="1" fitToHeight="0"/>
   <headerFooter>
-    <oddFooter>&amp;L&amp;"Calibri,Italic"Explore Excel&amp;R&amp;"Calibri,Italic"Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;9Explore Excel&amp;R&amp;9Page &amp;P of &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
--- a/public/downloads/invoice-template.xlsx
+++ b/public/downloads/invoice-template.xlsx
@@ -25,7 +25,7 @@
     <t>What this does</t>
   </si>
   <si>
-    <t>Produces one printable invoice that totals itself and calculates VAT, plus a log of what you have sent.</t>
+    <t>Produces one printable invoice that totals itself and calculates sales tax, plus a log of what you have sent.</t>
   </si>
   <si>
     <t/>
@@ -40,16 +40,16 @@
     <t>2. On the Invoice sheet, fill the cream cells: client block, invoice number and date.</t>
   </si>
   <si>
-    <t>3. Enter the line items. Amount, subtotal, VAT and total all calculate.</t>
-  </si>
-  <si>
-    <t>4. Print to PDF. The page is already set to fit one sheet of A4 portrait.</t>
-  </si>
-  <si>
-    <t>VAT</t>
-  </si>
-  <si>
-    <t>The rate comes from the Settings sheet. Set it to 0 if you are not VAT registered — the line then shows zero rather than disappearing, which is the correct thing to show a client.</t>
+    <t>3. Enter the line items. Amount, subtotal, sales tax and total all calculate.</t>
+  </si>
+  <si>
+    <t>4. Print to PDF. The page is already set to fit one sheet of US Letter portrait.</t>
+  </si>
+  <si>
+    <t>Sales tax</t>
+  </si>
+  <si>
+    <t>The rate comes from the Settings sheet. The 8.25% shown is a placeholder only — sales tax varies by state and often by city, so set the rate that applies where you are. Set it to 0 if you do not collect sales tax; the line then shows zero rather than disappearing, which is the correct thing to show a client.</t>
   </si>
   <si>
     <t>Keeping a record</t>
@@ -58,7 +58,7 @@
     <t>Add a row to the Invoice log as you send each one. The outstanding figure at the top totals everything still marked Unpaid.</t>
   </si>
   <si>
-    <t>Blue text on a cream background marks a cell you fill in. Black text is calculated — typing over one replaces the formula. Green shading is a heading or a total. This is the standard financial-modelling convention.</t>
+    <t>Blue text on a cream background marks a cell you fill in. Black text is calculated — typing over one replaces the formula. Green shading is a heading or a total. This is the standard financial-modeling convention.</t>
   </si>
   <si>
     <t>Your details</t>
@@ -76,55 +76,55 @@
     <t>Business name</t>
   </si>
   <si>
-    <t>Your Business Ltd</t>
+    <t>Your Business LLC</t>
   </si>
   <si>
     <t>Address line 1</t>
   </si>
   <si>
-    <t>12 Example Street</t>
+    <t>1200 Market Street</t>
   </si>
   <si>
     <t>Address line 2</t>
   </si>
   <si>
-    <t>Leeds</t>
-  </si>
-  <si>
-    <t>Postcode</t>
-  </si>
-  <si>
-    <t>LS1 1AA</t>
+    <t>Suite 400</t>
+  </si>
+  <si>
+    <t>City, State ZIP</t>
+  </si>
+  <si>
+    <t>Austin, TX 78701</t>
   </si>
   <si>
     <t>Email</t>
   </si>
   <si>
-    <t>hello@yourbusiness.co.uk</t>
+    <t>hello@yourbusiness.com</t>
   </si>
   <si>
     <t>Phone</t>
   </si>
   <si>
-    <t>0113 000 0000</t>
-  </si>
-  <si>
-    <t>VAT number</t>
-  </si>
-  <si>
-    <t>GB000000000</t>
-  </si>
-  <si>
-    <t>VAT rate</t>
+    <t>(512) 555-0100</t>
+  </si>
+  <si>
+    <t>EIN or Tax ID</t>
+  </si>
+  <si>
+    <t>00-0000000</t>
+  </si>
+  <si>
+    <t>Sales tax rate</t>
   </si>
   <si>
     <t>Bank account name</t>
   </si>
   <si>
-    <t>Sort code</t>
-  </si>
-  <si>
-    <t>00-00-00</t>
+    <t>Routing number</t>
+  </si>
+  <si>
+    <t>000000000</t>
   </si>
   <si>
     <t>Account number</t>
@@ -160,7 +160,7 @@
     <t>Client address</t>
   </si>
   <si>
-    <t>Town</t>
+    <t>Country</t>
   </si>
   <si>
     <t>Description</t>
@@ -217,7 +217,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>Northaero Ltd</t>
+    <t>Northaero Inc</t>
   </si>
   <si>
     <t>Unpaid</t>
@@ -236,9 +236,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="dd mmm yyyy"/>
-    <numFmt numFmtId="165" formatCode="&quot;£&quot;#,##0.00"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="0.000%"/>
+    <numFmt numFmtId="165" formatCode="mmm d, yyyy"/>
+    <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
   <fonts count="18" x14ac:knownFonts="1">
     <font>
@@ -428,7 +429,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="8" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -440,34 +441,34 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="8" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="8" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="12" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="12" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="17" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="17" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -931,7 +932,7 @@
   </sheetData>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" fitToWidth="1" fitToHeight="0"/>
+  <pageSetup paperSize="1" orientation="portrait" fitToWidth="1" fitToHeight="0"/>
   <headerFooter>
     <oddFooter>&amp;L&amp;9Explore Excel&amp;R&amp;9Page &amp;P of &amp;N</oddFooter>
   </headerFooter>
@@ -1032,7 +1033,7 @@
         <v>33</v>
       </c>
       <c r="B12" s="12">
-        <v>0.2</v>
+        <v>0.0825</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -1070,7 +1071,7 @@
   </sheetData>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" fitToWidth="1" fitToHeight="0"/>
+  <pageSetup paperSize="1" orientation="portrait" fitToWidth="1" fitToHeight="0"/>
   <headerFooter>
     <oddFooter>&amp;L&amp;9Explore Excel&amp;R&amp;9Page &amp;P of &amp;N</oddFooter>
   </headerFooter>
@@ -1155,12 +1156,12 @@
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="21" t="s">
-        <v>48</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="21" t="s">
-        <v>25</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13" ht="26" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1360,7 +1361,7 @@
   </sheetData>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" fitToWidth="1" fitToHeight="0"/>
+  <pageSetup paperSize="1" orientation="portrait" fitToWidth="1" fitToHeight="0"/>
   <headerFooter>
     <oddFooter>&amp;L&amp;9Explore Excel&amp;R&amp;9Page &amp;P of &amp;N</oddFooter>
   </headerFooter>
@@ -2273,7 +2274,7 @@
   </dataValidations>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" fitToWidth="1" fitToHeight="0"/>
+  <pageSetup paperSize="1" orientation="portrait" fitToWidth="1" fitToHeight="0"/>
   <headerFooter>
     <oddFooter>&amp;L&amp;9Explore Excel&amp;R&amp;9Page &amp;P of &amp;N</oddFooter>
   </headerFooter>

--- a/public/downloads/invoice-template.xlsx
+++ b/public/downloads/invoice-template.xlsx
@@ -14,23 +14,26 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="74">
+  <si>
+    <t>How this workbook works</t>
+  </si>
+  <si>
+    <t>Explore Excel  ·  exploreexcel.com</t>
+  </si>
+  <si>
+    <t>What this is</t>
+  </si>
   <si>
     <t>Invoice template</t>
   </si>
   <si>
-    <t>How to use this template</t>
-  </si>
-  <si>
     <t>What this does</t>
   </si>
   <si>
     <t>Produces one printable invoice that totals itself and calculates sales tax, plus a log of what you have sent.</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>Using it</t>
   </si>
   <si>
@@ -58,13 +61,16 @@
     <t>Add a row to the Invoice log as you send each one. The outstanding figure at the top totals everything still marked Unpaid.</t>
   </si>
   <si>
-    <t>Blue text on a cream background marks a cell you fill in. Black text is calculated — typing over one replaces the formula. Green shading is a heading or a total. This is the standard financial-modeling convention.</t>
+    <t>Reading the colors</t>
+  </si>
+  <si>
+    <t>Blue figures are yours to type over. Black figures are calculated — typing over one replaces the formula. Green shading is a heading or a total. This is the standard financial-modeling convention, so anyone in a finance or audit role will read it without being told.</t>
   </si>
   <si>
     <t>Your details</t>
   </si>
   <si>
-    <t>Entered once, used on every invoice</t>
+    <t>Explore Excel  ·  exploreexcel.com  ·  Entered once, used on every invoice</t>
   </si>
   <si>
     <t>Field</t>
@@ -199,7 +205,7 @@
     <t>Invoice log</t>
   </si>
   <si>
-    <t>One row per invoice sent</t>
+    <t>Explore Excel  ·  exploreexcel.com  ·  One row per invoice sent</t>
   </si>
   <si>
     <t>OUTSTANDING</t>
@@ -238,10 +244,10 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.000%"/>
-    <numFmt numFmtId="165" formatCode="mmm d, yyyy"/>
-    <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="165" formatCode="dd-mmm-yy"/>
+    <numFmt numFmtId="166" formatCode="#,##0;(#,##0);-"/>
   </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -251,15 +257,14 @@
     </font>
     <font>
       <b/>
-      <color rgb="FF0A4A3A"/>
-      <sz val="15"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="16"/>
       <name val="Arial"/>
     </font>
     <font>
-      <i/>
-      <color rgb="FF4A4A48"/>
-      <sz val="10"/>
-      <name val="Calibri"/>
+      <color rgb="FFC6E4D9"/>
+      <sz val="9"/>
+      <name val="Arial"/>
     </font>
     <font>
       <b/>
@@ -270,13 +275,7 @@
     <font>
       <color rgb="FF141414"/>
       <sz val="10"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <i/>
-      <color rgb="FF4A4A48"/>
-      <sz val="9"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
     </font>
     <font>
       <b/>
@@ -288,12 +287,12 @@
       <b/>
       <color rgb="FF0A4A3A"/>
       <sz val="10"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
     </font>
     <font>
       <color rgb="FF0000FF"/>
       <sz val="10"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
     </font>
     <font>
       <b/>
@@ -310,7 +309,7 @@
     <font>
       <color rgb="FF4A4A48"/>
       <sz val="10"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
     </font>
     <font>
       <b/>
@@ -319,26 +318,26 @@
       <name val="Arial"/>
     </font>
     <font>
-      <b/>
-      <color rgb="FF0A4A3A"/>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
       <color rgb="FF4A4A48"/>
       <sz val="9"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
     </font>
     <font>
       <color rgb="FF141414"/>
       <sz val="9"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <i/>
+      <color rgb="FF4A4A48"/>
+      <sz val="9"/>
+      <name val="Arial"/>
     </font>
     <font>
       <b/>
       <color rgb="FF4A4A48"/>
       <sz val="9"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
     </font>
     <font>
       <b/>
@@ -356,11 +355,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE1F5EE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF0F6E56"/>
       </patternFill>
     </fill>
@@ -372,6 +366,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFAFAF8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE1F5EE"/>
       </patternFill>
     </fill>
   </fills>
@@ -402,73 +401,62 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="centerContinuous" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="centerContinuous"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="8" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="11" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="17" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="16" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -835,98 +823,100 @@
     <tabColor rgb="FF4A4A48"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:B20"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="3" customWidth="1"/>
-    <col min="2" max="2" width="94" customWidth="1"/>
+    <col min="1" max="1" width="40" customWidth="1"/>
+    <col min="2" max="3" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+    <row r="1" ht="25.5" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+    </row>
+    <row r="2" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
       <c r="B2" s="2"/>
-    </row>
-    <row r="3" ht="16" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="4"/>
-    </row>
-    <row r="5" ht="22" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B5" s="5" t="s">
+      <c r="C2" s="2"/>
+    </row>
+    <row r="4" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="6" ht="30" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B6" s="6" t="s">
+    <row r="5" ht="33.75" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" ht="16" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B7" s="6" t="s">
+    <row r="7" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="8" ht="22" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B8" s="5" t="s">
+    <row r="8" ht="33.75" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9" ht="16" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B9" s="6" t="s">
+    <row r="10" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="10" ht="16" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B10" s="6" t="s">
+    <row r="11" ht="33.75" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="11" ht="16" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B11" s="6" t="s">
+    <row r="13" ht="33.75" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="12" ht="16" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B12" s="6" t="s">
+    <row r="15" ht="33.75" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="13" ht="16" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B13" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="14" ht="22" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B14" s="5" t="s">
+    <row r="17" ht="33.75" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" ht="30" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B15" s="6" t="s">
+    <row r="19" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="16" ht="16" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B16" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="17" ht="22" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B17" s="5" t="s">
+    <row r="20" ht="48" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" s="4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="18" ht="30" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B18" s="6" t="s">
+    <row r="22" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="20" ht="30" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B20" s="7" t="s">
+    <row r="23" ht="33.75" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" s="4" t="s">
         <v>14</v>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26" ht="48" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" s="4" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -952,119 +942,119 @@
     <col min="2" max="2" width="44" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" ht="25.5" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B1" s="2"/>
-    </row>
-    <row r="2" ht="16" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B2" s="4"/>
-    </row>
-    <row r="4" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B1" s="1"/>
+    </row>
+    <row r="2" ht="15" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
         <v>18</v>
       </c>
+      <c r="B2" s="2"/>
+    </row>
+    <row r="4" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="B5" s="10" t="s">
-        <v>20</v>
+      <c r="A5" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="B6" s="10" t="s">
+      <c r="A6" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B12" s="9">
+        <v>0.0825</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B13" s="7" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="B7" s="10" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="B8" s="10" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="B9" s="10" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="B10" s="10" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="B11" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="B12" s="12">
-        <v>0.0825</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="B13" s="10" t="s">
-        <v>20</v>
-      </c>
-    </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="B14" s="10" t="s">
-        <v>36</v>
+      <c r="A14" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="B15" s="10" t="s">
-        <v>38</v>
+      <c r="A15" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="B16" s="10">
+      <c r="A16" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="B16" s="7">
         <v>30</v>
       </c>
     </row>
@@ -1094,267 +1084,267 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="13">
+      <c r="A1" s="10">
         <f>Settings!B5</f>
       </c>
-      <c r="D1" s="14" t="s">
-        <v>40</v>
+      <c r="D1" s="11" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="15">
+      <c r="A2" s="12">
         <f>Settings!B6</f>
       </c>
-      <c r="C2" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="D2" s="17" t="s">
-        <v>42</v>
+      <c r="C2" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="D2" s="14" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="15">
+      <c r="A3" s="12">
         <f>Settings!B7</f>
       </c>
-      <c r="C3" s="16" t="s">
-        <v>43</v>
-      </c>
-      <c r="D3" s="18">
+      <c r="C3" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="D3" s="15">
         <v>46030</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="15">
+      <c r="A4" s="12">
         <f>Settings!B8</f>
       </c>
-      <c r="C4" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="D4" s="19">
+      <c r="C4" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="D4" s="16">
         <f>D3+Settings!$B$16</f>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" s="15">
+      <c r="A5" s="12">
         <f>Settings!B9</f>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" s="20" t="s">
-        <v>45</v>
+      <c r="A7" s="17" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" s="21" t="s">
-        <v>46</v>
+      <c r="A8" s="18" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" s="21" t="s">
-        <v>47</v>
+      <c r="A9" s="18" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" s="21" t="s">
-        <v>25</v>
+      <c r="A10" s="18" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" s="21" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="13" ht="26" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="B13" s="8" t="s">
+      <c r="A11" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="C13" s="8" t="s">
+    </row>
+    <row r="13" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="D13" s="8" t="s">
+      <c r="B13" s="5" t="s">
         <v>52</v>
       </c>
+      <c r="C13" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="B14" s="10">
+      <c r="A14" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B14" s="7">
         <v>12</v>
       </c>
-      <c r="C14" s="22">
+      <c r="C14" s="19">
         <v>65</v>
       </c>
-      <c r="D14" s="23">
+      <c r="D14" s="20">
         <f>IF(B14="","",B14*C14)</f>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="B15" s="10">
+      <c r="A15" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="B15" s="7">
         <v>1</v>
       </c>
-      <c r="C15" s="22">
+      <c r="C15" s="19">
         <v>900</v>
       </c>
-      <c r="D15" s="24">
+      <c r="D15" s="21">
         <f>IF(B15="","",B15*C15)</f>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="B16" s="10">
+      <c r="A16" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="B16" s="7">
         <v>2</v>
       </c>
-      <c r="C16" s="22">
+      <c r="C16" s="19">
         <v>350</v>
       </c>
-      <c r="D16" s="23">
+      <c r="D16" s="20">
         <f>IF(B16="","",B16*C16)</f>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="10"/>
-      <c r="B17" s="10"/>
-      <c r="C17" s="22"/>
-      <c r="D17" s="24">
+      <c r="A17" s="7"/>
+      <c r="B17" s="7"/>
+      <c r="C17" s="19"/>
+      <c r="D17" s="21">
         <f>IF(B17="","",B17*C17)</f>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="10"/>
-      <c r="B18" s="10"/>
-      <c r="C18" s="22"/>
-      <c r="D18" s="23">
+      <c r="A18" s="7"/>
+      <c r="B18" s="7"/>
+      <c r="C18" s="19"/>
+      <c r="D18" s="20">
         <f>IF(B18="","",B18*C18)</f>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="10"/>
-      <c r="B19" s="10"/>
-      <c r="C19" s="22"/>
-      <c r="D19" s="24">
+      <c r="A19" s="7"/>
+      <c r="B19" s="7"/>
+      <c r="C19" s="19"/>
+      <c r="D19" s="21">
         <f>IF(B19="","",B19*C19)</f>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="10"/>
-      <c r="B20" s="10"/>
-      <c r="C20" s="22"/>
-      <c r="D20" s="23">
+      <c r="A20" s="7"/>
+      <c r="B20" s="7"/>
+      <c r="C20" s="19"/>
+      <c r="D20" s="20">
         <f>IF(B20="","",B20*C20)</f>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="10"/>
-      <c r="B21" s="10"/>
-      <c r="C21" s="22"/>
-      <c r="D21" s="24">
+      <c r="A21" s="7"/>
+      <c r="B21" s="7"/>
+      <c r="C21" s="19"/>
+      <c r="D21" s="21">
         <f>IF(B21="","",B21*C21)</f>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="10"/>
-      <c r="B22" s="10"/>
-      <c r="C22" s="22"/>
-      <c r="D22" s="23">
+      <c r="A22" s="7"/>
+      <c r="B22" s="7"/>
+      <c r="C22" s="19"/>
+      <c r="D22" s="20">
         <f>IF(B22="","",B22*C22)</f>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="10"/>
-      <c r="B23" s="10"/>
-      <c r="C23" s="22"/>
-      <c r="D23" s="24">
+      <c r="A23" s="7"/>
+      <c r="B23" s="7"/>
+      <c r="C23" s="19"/>
+      <c r="D23" s="21">
         <f>IF(B23="","",B23*C23)</f>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="10"/>
-      <c r="B24" s="10"/>
-      <c r="C24" s="22"/>
-      <c r="D24" s="23">
+      <c r="A24" s="7"/>
+      <c r="B24" s="7"/>
+      <c r="C24" s="19"/>
+      <c r="D24" s="20">
         <f>IF(B24="","",B24*C24)</f>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="10"/>
-      <c r="B25" s="10"/>
-      <c r="C25" s="22"/>
-      <c r="D25" s="24">
+      <c r="A25" s="7"/>
+      <c r="B25" s="7"/>
+      <c r="C25" s="19"/>
+      <c r="D25" s="21">
         <f>IF(B25="","",B25*C25)</f>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="10"/>
-      <c r="B26" s="10"/>
-      <c r="C26" s="22"/>
-      <c r="D26" s="23">
+      <c r="A26" s="7"/>
+      <c r="B26" s="7"/>
+      <c r="C26" s="19"/>
+      <c r="D26" s="20">
         <f>IF(B26="","",B26*C26)</f>
       </c>
     </row>
     <row r="27" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C27" s="25" t="s">
-        <v>56</v>
-      </c>
-      <c r="D27" s="23">
+      <c r="C27" s="22" t="s">
+        <v>58</v>
+      </c>
+      <c r="D27" s="20">
         <f>SUM(D14:D26)</f>
       </c>
     </row>
     <row r="28" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C28" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="D28" s="23">
+      <c r="C28" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="D28" s="20">
         <f>ROUND(D27*Settings!$B$12,2)</f>
       </c>
     </row>
     <row r="29" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C29" s="26" t="s">
-        <v>57</v>
-      </c>
-      <c r="D29" s="27">
+      <c r="C29" s="23" t="s">
+        <v>59</v>
+      </c>
+      <c r="D29" s="24">
         <f>D27+D28</f>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A31" s="28" t="s">
-        <v>58</v>
+      <c r="A31" s="25" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="29" t="s">
-        <v>59</v>
-      </c>
-      <c r="B32" s="30">
+      <c r="A32" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="B32" s="27">
         <f>Settings!B13</f>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="29" t="s">
-        <v>35</v>
-      </c>
-      <c r="B33" s="30">
+      <c r="A33" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="B33" s="27">
         <f>Settings!B14</f>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" s="29" t="s">
-        <v>37</v>
-      </c>
-      <c r="B34" s="30">
+      <c r="A34" s="26" t="s">
+        <v>39</v>
+      </c>
+      <c r="B34" s="27">
         <f>Settings!B15</f>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A36" s="31">
+      <c r="A36" s="28">
         <f>"Payment due within "&amp;Settings!$B$16&amp;" days of the invoice date."</f>
       </c>
     </row>
@@ -1383,879 +1373,879 @@
     <col min="6" max="6" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" ht="25.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-    </row>
-    <row r="2" ht="16" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
+        <v>62</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+    </row>
+    <row r="2" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" s="32" t="s">
-        <v>62</v>
+      <c r="A4" s="29" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" s="33">
+      <c r="A5" s="30">
         <f>SUMIFS(E8:E107,F8:F107,"Unpaid")</f>
       </c>
     </row>
-    <row r="7" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="D7" s="8" t="s">
+    <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="E7" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="F7" s="8" t="s">
+      <c r="C7" s="5" t="s">
         <v>66</v>
       </c>
+      <c r="D7" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="34" t="s">
-        <v>42</v>
-      </c>
-      <c r="B8" s="34" t="s">
-        <v>67</v>
-      </c>
-      <c r="C8" s="35">
+      <c r="A8" s="31" t="s">
+        <v>44</v>
+      </c>
+      <c r="B8" s="31" t="s">
+        <v>69</v>
+      </c>
+      <c r="C8" s="32">
         <v>46030</v>
       </c>
-      <c r="D8" s="35">
+      <c r="D8" s="32">
         <v>46060</v>
       </c>
-      <c r="E8" s="23">
+      <c r="E8" s="20">
         <v>2020</v>
       </c>
-      <c r="F8" s="34" t="s">
-        <v>68</v>
+      <c r="F8" s="31" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="36" t="s">
-        <v>69</v>
-      </c>
-      <c r="B9" s="36" t="s">
-        <v>70</v>
-      </c>
-      <c r="C9" s="37">
+      <c r="A9" s="33" t="s">
+        <v>71</v>
+      </c>
+      <c r="B9" s="33" t="s">
+        <v>72</v>
+      </c>
+      <c r="C9" s="34">
         <v>46033</v>
       </c>
-      <c r="D9" s="37">
+      <c r="D9" s="34">
         <v>46063</v>
       </c>
-      <c r="E9" s="24">
+      <c r="E9" s="21">
         <v>780</v>
       </c>
-      <c r="F9" s="36" t="s">
-        <v>71</v>
+      <c r="F9" s="33" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="34"/>
-      <c r="B10" s="34"/>
-      <c r="C10" s="35"/>
-      <c r="D10" s="35"/>
-      <c r="E10" s="23"/>
-      <c r="F10" s="34"/>
+      <c r="A10" s="31"/>
+      <c r="B10" s="31"/>
+      <c r="C10" s="32"/>
+      <c r="D10" s="32"/>
+      <c r="E10" s="20"/>
+      <c r="F10" s="31"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="36"/>
-      <c r="B11" s="36"/>
-      <c r="C11" s="37"/>
-      <c r="D11" s="37"/>
-      <c r="E11" s="24"/>
-      <c r="F11" s="36"/>
+      <c r="A11" s="33"/>
+      <c r="B11" s="33"/>
+      <c r="C11" s="34"/>
+      <c r="D11" s="34"/>
+      <c r="E11" s="21"/>
+      <c r="F11" s="33"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="34"/>
-      <c r="B12" s="34"/>
-      <c r="C12" s="35"/>
-      <c r="D12" s="35"/>
-      <c r="E12" s="23"/>
-      <c r="F12" s="34"/>
+      <c r="A12" s="31"/>
+      <c r="B12" s="31"/>
+      <c r="C12" s="32"/>
+      <c r="D12" s="32"/>
+      <c r="E12" s="20"/>
+      <c r="F12" s="31"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="36"/>
-      <c r="B13" s="36"/>
-      <c r="C13" s="37"/>
-      <c r="D13" s="37"/>
-      <c r="E13" s="24"/>
-      <c r="F13" s="36"/>
+      <c r="A13" s="33"/>
+      <c r="B13" s="33"/>
+      <c r="C13" s="34"/>
+      <c r="D13" s="34"/>
+      <c r="E13" s="21"/>
+      <c r="F13" s="33"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="34"/>
-      <c r="B14" s="34"/>
-      <c r="C14" s="35"/>
-      <c r="D14" s="35"/>
-      <c r="E14" s="23"/>
-      <c r="F14" s="34"/>
+      <c r="A14" s="31"/>
+      <c r="B14" s="31"/>
+      <c r="C14" s="32"/>
+      <c r="D14" s="32"/>
+      <c r="E14" s="20"/>
+      <c r="F14" s="31"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="36"/>
-      <c r="B15" s="36"/>
-      <c r="C15" s="37"/>
-      <c r="D15" s="37"/>
-      <c r="E15" s="24"/>
-      <c r="F15" s="36"/>
+      <c r="A15" s="33"/>
+      <c r="B15" s="33"/>
+      <c r="C15" s="34"/>
+      <c r="D15" s="34"/>
+      <c r="E15" s="21"/>
+      <c r="F15" s="33"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="34"/>
-      <c r="B16" s="34"/>
-      <c r="C16" s="35"/>
-      <c r="D16" s="35"/>
-      <c r="E16" s="23"/>
-      <c r="F16" s="34"/>
+      <c r="A16" s="31"/>
+      <c r="B16" s="31"/>
+      <c r="C16" s="32"/>
+      <c r="D16" s="32"/>
+      <c r="E16" s="20"/>
+      <c r="F16" s="31"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="36"/>
-      <c r="B17" s="36"/>
-      <c r="C17" s="37"/>
-      <c r="D17" s="37"/>
-      <c r="E17" s="24"/>
-      <c r="F17" s="36"/>
+      <c r="A17" s="33"/>
+      <c r="B17" s="33"/>
+      <c r="C17" s="34"/>
+      <c r="D17" s="34"/>
+      <c r="E17" s="21"/>
+      <c r="F17" s="33"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="34"/>
-      <c r="B18" s="34"/>
-      <c r="C18" s="35"/>
-      <c r="D18" s="35"/>
-      <c r="E18" s="23"/>
-      <c r="F18" s="34"/>
+      <c r="A18" s="31"/>
+      <c r="B18" s="31"/>
+      <c r="C18" s="32"/>
+      <c r="D18" s="32"/>
+      <c r="E18" s="20"/>
+      <c r="F18" s="31"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="36"/>
-      <c r="B19" s="36"/>
-      <c r="C19" s="37"/>
-      <c r="D19" s="37"/>
-      <c r="E19" s="24"/>
-      <c r="F19" s="36"/>
+      <c r="A19" s="33"/>
+      <c r="B19" s="33"/>
+      <c r="C19" s="34"/>
+      <c r="D19" s="34"/>
+      <c r="E19" s="21"/>
+      <c r="F19" s="33"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="34"/>
-      <c r="B20" s="34"/>
-      <c r="C20" s="35"/>
-      <c r="D20" s="35"/>
-      <c r="E20" s="23"/>
-      <c r="F20" s="34"/>
+      <c r="A20" s="31"/>
+      <c r="B20" s="31"/>
+      <c r="C20" s="32"/>
+      <c r="D20" s="32"/>
+      <c r="E20" s="20"/>
+      <c r="F20" s="31"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="36"/>
-      <c r="B21" s="36"/>
-      <c r="C21" s="37"/>
-      <c r="D21" s="37"/>
-      <c r="E21" s="24"/>
-      <c r="F21" s="36"/>
+      <c r="A21" s="33"/>
+      <c r="B21" s="33"/>
+      <c r="C21" s="34"/>
+      <c r="D21" s="34"/>
+      <c r="E21" s="21"/>
+      <c r="F21" s="33"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="34"/>
-      <c r="B22" s="34"/>
-      <c r="C22" s="35"/>
-      <c r="D22" s="35"/>
-      <c r="E22" s="23"/>
-      <c r="F22" s="34"/>
+      <c r="A22" s="31"/>
+      <c r="B22" s="31"/>
+      <c r="C22" s="32"/>
+      <c r="D22" s="32"/>
+      <c r="E22" s="20"/>
+      <c r="F22" s="31"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="36"/>
-      <c r="B23" s="36"/>
-      <c r="C23" s="37"/>
-      <c r="D23" s="37"/>
-      <c r="E23" s="24"/>
-      <c r="F23" s="36"/>
+      <c r="A23" s="33"/>
+      <c r="B23" s="33"/>
+      <c r="C23" s="34"/>
+      <c r="D23" s="34"/>
+      <c r="E23" s="21"/>
+      <c r="F23" s="33"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="34"/>
-      <c r="B24" s="34"/>
-      <c r="C24" s="35"/>
-      <c r="D24" s="35"/>
-      <c r="E24" s="23"/>
-      <c r="F24" s="34"/>
+      <c r="A24" s="31"/>
+      <c r="B24" s="31"/>
+      <c r="C24" s="32"/>
+      <c r="D24" s="32"/>
+      <c r="E24" s="20"/>
+      <c r="F24" s="31"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="36"/>
-      <c r="B25" s="36"/>
-      <c r="C25" s="37"/>
-      <c r="D25" s="37"/>
-      <c r="E25" s="24"/>
-      <c r="F25" s="36"/>
+      <c r="A25" s="33"/>
+      <c r="B25" s="33"/>
+      <c r="C25" s="34"/>
+      <c r="D25" s="34"/>
+      <c r="E25" s="21"/>
+      <c r="F25" s="33"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="34"/>
-      <c r="B26" s="34"/>
-      <c r="C26" s="35"/>
-      <c r="D26" s="35"/>
-      <c r="E26" s="23"/>
-      <c r="F26" s="34"/>
+      <c r="A26" s="31"/>
+      <c r="B26" s="31"/>
+      <c r="C26" s="32"/>
+      <c r="D26" s="32"/>
+      <c r="E26" s="20"/>
+      <c r="F26" s="31"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="36"/>
-      <c r="B27" s="36"/>
-      <c r="C27" s="37"/>
-      <c r="D27" s="37"/>
-      <c r="E27" s="24"/>
-      <c r="F27" s="36"/>
+      <c r="A27" s="33"/>
+      <c r="B27" s="33"/>
+      <c r="C27" s="34"/>
+      <c r="D27" s="34"/>
+      <c r="E27" s="21"/>
+      <c r="F27" s="33"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="34"/>
-      <c r="B28" s="34"/>
-      <c r="C28" s="35"/>
-      <c r="D28" s="35"/>
-      <c r="E28" s="23"/>
-      <c r="F28" s="34"/>
+      <c r="A28" s="31"/>
+      <c r="B28" s="31"/>
+      <c r="C28" s="32"/>
+      <c r="D28" s="32"/>
+      <c r="E28" s="20"/>
+      <c r="F28" s="31"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="36"/>
-      <c r="B29" s="36"/>
-      <c r="C29" s="37"/>
-      <c r="D29" s="37"/>
-      <c r="E29" s="24"/>
-      <c r="F29" s="36"/>
+      <c r="A29" s="33"/>
+      <c r="B29" s="33"/>
+      <c r="C29" s="34"/>
+      <c r="D29" s="34"/>
+      <c r="E29" s="21"/>
+      <c r="F29" s="33"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="34"/>
-      <c r="B30" s="34"/>
-      <c r="C30" s="35"/>
-      <c r="D30" s="35"/>
-      <c r="E30" s="23"/>
-      <c r="F30" s="34"/>
+      <c r="A30" s="31"/>
+      <c r="B30" s="31"/>
+      <c r="C30" s="32"/>
+      <c r="D30" s="32"/>
+      <c r="E30" s="20"/>
+      <c r="F30" s="31"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="36"/>
-      <c r="B31" s="36"/>
-      <c r="C31" s="37"/>
-      <c r="D31" s="37"/>
-      <c r="E31" s="24"/>
-      <c r="F31" s="36"/>
+      <c r="A31" s="33"/>
+      <c r="B31" s="33"/>
+      <c r="C31" s="34"/>
+      <c r="D31" s="34"/>
+      <c r="E31" s="21"/>
+      <c r="F31" s="33"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="34"/>
-      <c r="B32" s="34"/>
-      <c r="C32" s="35"/>
-      <c r="D32" s="35"/>
-      <c r="E32" s="23"/>
-      <c r="F32" s="34"/>
+      <c r="A32" s="31"/>
+      <c r="B32" s="31"/>
+      <c r="C32" s="32"/>
+      <c r="D32" s="32"/>
+      <c r="E32" s="20"/>
+      <c r="F32" s="31"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="36"/>
-      <c r="B33" s="36"/>
-      <c r="C33" s="37"/>
-      <c r="D33" s="37"/>
-      <c r="E33" s="24"/>
-      <c r="F33" s="36"/>
+      <c r="A33" s="33"/>
+      <c r="B33" s="33"/>
+      <c r="C33" s="34"/>
+      <c r="D33" s="34"/>
+      <c r="E33" s="21"/>
+      <c r="F33" s="33"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="34"/>
-      <c r="B34" s="34"/>
-      <c r="C34" s="35"/>
-      <c r="D34" s="35"/>
-      <c r="E34" s="23"/>
-      <c r="F34" s="34"/>
+      <c r="A34" s="31"/>
+      <c r="B34" s="31"/>
+      <c r="C34" s="32"/>
+      <c r="D34" s="32"/>
+      <c r="E34" s="20"/>
+      <c r="F34" s="31"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="36"/>
-      <c r="B35" s="36"/>
-      <c r="C35" s="37"/>
-      <c r="D35" s="37"/>
-      <c r="E35" s="24"/>
-      <c r="F35" s="36"/>
+      <c r="A35" s="33"/>
+      <c r="B35" s="33"/>
+      <c r="C35" s="34"/>
+      <c r="D35" s="34"/>
+      <c r="E35" s="21"/>
+      <c r="F35" s="33"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="34"/>
-      <c r="B36" s="34"/>
-      <c r="C36" s="35"/>
-      <c r="D36" s="35"/>
-      <c r="E36" s="23"/>
-      <c r="F36" s="34"/>
+      <c r="A36" s="31"/>
+      <c r="B36" s="31"/>
+      <c r="C36" s="32"/>
+      <c r="D36" s="32"/>
+      <c r="E36" s="20"/>
+      <c r="F36" s="31"/>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="36"/>
-      <c r="B37" s="36"/>
-      <c r="C37" s="37"/>
-      <c r="D37" s="37"/>
-      <c r="E37" s="24"/>
-      <c r="F37" s="36"/>
+      <c r="A37" s="33"/>
+      <c r="B37" s="33"/>
+      <c r="C37" s="34"/>
+      <c r="D37" s="34"/>
+      <c r="E37" s="21"/>
+      <c r="F37" s="33"/>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="34"/>
-      <c r="B38" s="34"/>
-      <c r="C38" s="35"/>
-      <c r="D38" s="35"/>
-      <c r="E38" s="23"/>
-      <c r="F38" s="34"/>
+      <c r="A38" s="31"/>
+      <c r="B38" s="31"/>
+      <c r="C38" s="32"/>
+      <c r="D38" s="32"/>
+      <c r="E38" s="20"/>
+      <c r="F38" s="31"/>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="36"/>
-      <c r="B39" s="36"/>
-      <c r="C39" s="37"/>
-      <c r="D39" s="37"/>
-      <c r="E39" s="24"/>
-      <c r="F39" s="36"/>
+      <c r="A39" s="33"/>
+      <c r="B39" s="33"/>
+      <c r="C39" s="34"/>
+      <c r="D39" s="34"/>
+      <c r="E39" s="21"/>
+      <c r="F39" s="33"/>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="34"/>
-      <c r="B40" s="34"/>
-      <c r="C40" s="35"/>
-      <c r="D40" s="35"/>
-      <c r="E40" s="23"/>
-      <c r="F40" s="34"/>
+      <c r="A40" s="31"/>
+      <c r="B40" s="31"/>
+      <c r="C40" s="32"/>
+      <c r="D40" s="32"/>
+      <c r="E40" s="20"/>
+      <c r="F40" s="31"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="36"/>
-      <c r="B41" s="36"/>
-      <c r="C41" s="37"/>
-      <c r="D41" s="37"/>
-      <c r="E41" s="24"/>
-      <c r="F41" s="36"/>
+      <c r="A41" s="33"/>
+      <c r="B41" s="33"/>
+      <c r="C41" s="34"/>
+      <c r="D41" s="34"/>
+      <c r="E41" s="21"/>
+      <c r="F41" s="33"/>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="34"/>
-      <c r="B42" s="34"/>
-      <c r="C42" s="35"/>
-      <c r="D42" s="35"/>
-      <c r="E42" s="23"/>
-      <c r="F42" s="34"/>
+      <c r="A42" s="31"/>
+      <c r="B42" s="31"/>
+      <c r="C42" s="32"/>
+      <c r="D42" s="32"/>
+      <c r="E42" s="20"/>
+      <c r="F42" s="31"/>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="36"/>
-      <c r="B43" s="36"/>
-      <c r="C43" s="37"/>
-      <c r="D43" s="37"/>
-      <c r="E43" s="24"/>
-      <c r="F43" s="36"/>
+      <c r="A43" s="33"/>
+      <c r="B43" s="33"/>
+      <c r="C43" s="34"/>
+      <c r="D43" s="34"/>
+      <c r="E43" s="21"/>
+      <c r="F43" s="33"/>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="34"/>
-      <c r="B44" s="34"/>
-      <c r="C44" s="35"/>
-      <c r="D44" s="35"/>
-      <c r="E44" s="23"/>
-      <c r="F44" s="34"/>
+      <c r="A44" s="31"/>
+      <c r="B44" s="31"/>
+      <c r="C44" s="32"/>
+      <c r="D44" s="32"/>
+      <c r="E44" s="20"/>
+      <c r="F44" s="31"/>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="36"/>
-      <c r="B45" s="36"/>
-      <c r="C45" s="37"/>
-      <c r="D45" s="37"/>
-      <c r="E45" s="24"/>
-      <c r="F45" s="36"/>
+      <c r="A45" s="33"/>
+      <c r="B45" s="33"/>
+      <c r="C45" s="34"/>
+      <c r="D45" s="34"/>
+      <c r="E45" s="21"/>
+      <c r="F45" s="33"/>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="34"/>
-      <c r="B46" s="34"/>
-      <c r="C46" s="35"/>
-      <c r="D46" s="35"/>
-      <c r="E46" s="23"/>
-      <c r="F46" s="34"/>
+      <c r="A46" s="31"/>
+      <c r="B46" s="31"/>
+      <c r="C46" s="32"/>
+      <c r="D46" s="32"/>
+      <c r="E46" s="20"/>
+      <c r="F46" s="31"/>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="36"/>
-      <c r="B47" s="36"/>
-      <c r="C47" s="37"/>
-      <c r="D47" s="37"/>
-      <c r="E47" s="24"/>
-      <c r="F47" s="36"/>
+      <c r="A47" s="33"/>
+      <c r="B47" s="33"/>
+      <c r="C47" s="34"/>
+      <c r="D47" s="34"/>
+      <c r="E47" s="21"/>
+      <c r="F47" s="33"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" s="34"/>
-      <c r="B48" s="34"/>
-      <c r="C48" s="35"/>
-      <c r="D48" s="35"/>
-      <c r="E48" s="23"/>
-      <c r="F48" s="34"/>
+      <c r="A48" s="31"/>
+      <c r="B48" s="31"/>
+      <c r="C48" s="32"/>
+      <c r="D48" s="32"/>
+      <c r="E48" s="20"/>
+      <c r="F48" s="31"/>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" s="36"/>
-      <c r="B49" s="36"/>
-      <c r="C49" s="37"/>
-      <c r="D49" s="37"/>
-      <c r="E49" s="24"/>
-      <c r="F49" s="36"/>
+      <c r="A49" s="33"/>
+      <c r="B49" s="33"/>
+      <c r="C49" s="34"/>
+      <c r="D49" s="34"/>
+      <c r="E49" s="21"/>
+      <c r="F49" s="33"/>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="34"/>
-      <c r="B50" s="34"/>
-      <c r="C50" s="35"/>
-      <c r="D50" s="35"/>
-      <c r="E50" s="23"/>
-      <c r="F50" s="34"/>
+      <c r="A50" s="31"/>
+      <c r="B50" s="31"/>
+      <c r="C50" s="32"/>
+      <c r="D50" s="32"/>
+      <c r="E50" s="20"/>
+      <c r="F50" s="31"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" s="36"/>
-      <c r="B51" s="36"/>
-      <c r="C51" s="37"/>
-      <c r="D51" s="37"/>
-      <c r="E51" s="24"/>
-      <c r="F51" s="36"/>
+      <c r="A51" s="33"/>
+      <c r="B51" s="33"/>
+      <c r="C51" s="34"/>
+      <c r="D51" s="34"/>
+      <c r="E51" s="21"/>
+      <c r="F51" s="33"/>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52" s="34"/>
-      <c r="B52" s="34"/>
-      <c r="C52" s="35"/>
-      <c r="D52" s="35"/>
-      <c r="E52" s="23"/>
-      <c r="F52" s="34"/>
+      <c r="A52" s="31"/>
+      <c r="B52" s="31"/>
+      <c r="C52" s="32"/>
+      <c r="D52" s="32"/>
+      <c r="E52" s="20"/>
+      <c r="F52" s="31"/>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53" s="36"/>
-      <c r="B53" s="36"/>
-      <c r="C53" s="37"/>
-      <c r="D53" s="37"/>
-      <c r="E53" s="24"/>
-      <c r="F53" s="36"/>
+      <c r="A53" s="33"/>
+      <c r="B53" s="33"/>
+      <c r="C53" s="34"/>
+      <c r="D53" s="34"/>
+      <c r="E53" s="21"/>
+      <c r="F53" s="33"/>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" s="34"/>
-      <c r="B54" s="34"/>
-      <c r="C54" s="35"/>
-      <c r="D54" s="35"/>
-      <c r="E54" s="23"/>
-      <c r="F54" s="34"/>
+      <c r="A54" s="31"/>
+      <c r="B54" s="31"/>
+      <c r="C54" s="32"/>
+      <c r="D54" s="32"/>
+      <c r="E54" s="20"/>
+      <c r="F54" s="31"/>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55" s="36"/>
-      <c r="B55" s="36"/>
-      <c r="C55" s="37"/>
-      <c r="D55" s="37"/>
-      <c r="E55" s="24"/>
-      <c r="F55" s="36"/>
+      <c r="A55" s="33"/>
+      <c r="B55" s="33"/>
+      <c r="C55" s="34"/>
+      <c r="D55" s="34"/>
+      <c r="E55" s="21"/>
+      <c r="F55" s="33"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" s="34"/>
-      <c r="B56" s="34"/>
-      <c r="C56" s="35"/>
-      <c r="D56" s="35"/>
-      <c r="E56" s="23"/>
-      <c r="F56" s="34"/>
+      <c r="A56" s="31"/>
+      <c r="B56" s="31"/>
+      <c r="C56" s="32"/>
+      <c r="D56" s="32"/>
+      <c r="E56" s="20"/>
+      <c r="F56" s="31"/>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A57" s="36"/>
-      <c r="B57" s="36"/>
-      <c r="C57" s="37"/>
-      <c r="D57" s="37"/>
-      <c r="E57" s="24"/>
-      <c r="F57" s="36"/>
+      <c r="A57" s="33"/>
+      <c r="B57" s="33"/>
+      <c r="C57" s="34"/>
+      <c r="D57" s="34"/>
+      <c r="E57" s="21"/>
+      <c r="F57" s="33"/>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A58" s="34"/>
-      <c r="B58" s="34"/>
-      <c r="C58" s="35"/>
-      <c r="D58" s="35"/>
-      <c r="E58" s="23"/>
-      <c r="F58" s="34"/>
+      <c r="A58" s="31"/>
+      <c r="B58" s="31"/>
+      <c r="C58" s="32"/>
+      <c r="D58" s="32"/>
+      <c r="E58" s="20"/>
+      <c r="F58" s="31"/>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A59" s="36"/>
-      <c r="B59" s="36"/>
-      <c r="C59" s="37"/>
-      <c r="D59" s="37"/>
-      <c r="E59" s="24"/>
-      <c r="F59" s="36"/>
+      <c r="A59" s="33"/>
+      <c r="B59" s="33"/>
+      <c r="C59" s="34"/>
+      <c r="D59" s="34"/>
+      <c r="E59" s="21"/>
+      <c r="F59" s="33"/>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="34"/>
-      <c r="B60" s="34"/>
-      <c r="C60" s="35"/>
-      <c r="D60" s="35"/>
-      <c r="E60" s="23"/>
-      <c r="F60" s="34"/>
+      <c r="A60" s="31"/>
+      <c r="B60" s="31"/>
+      <c r="C60" s="32"/>
+      <c r="D60" s="32"/>
+      <c r="E60" s="20"/>
+      <c r="F60" s="31"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="36"/>
-      <c r="B61" s="36"/>
-      <c r="C61" s="37"/>
-      <c r="D61" s="37"/>
-      <c r="E61" s="24"/>
-      <c r="F61" s="36"/>
+      <c r="A61" s="33"/>
+      <c r="B61" s="33"/>
+      <c r="C61" s="34"/>
+      <c r="D61" s="34"/>
+      <c r="E61" s="21"/>
+      <c r="F61" s="33"/>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="34"/>
-      <c r="B62" s="34"/>
-      <c r="C62" s="35"/>
-      <c r="D62" s="35"/>
-      <c r="E62" s="23"/>
-      <c r="F62" s="34"/>
+      <c r="A62" s="31"/>
+      <c r="B62" s="31"/>
+      <c r="C62" s="32"/>
+      <c r="D62" s="32"/>
+      <c r="E62" s="20"/>
+      <c r="F62" s="31"/>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A63" s="36"/>
-      <c r="B63" s="36"/>
-      <c r="C63" s="37"/>
-      <c r="D63" s="37"/>
-      <c r="E63" s="24"/>
-      <c r="F63" s="36"/>
+      <c r="A63" s="33"/>
+      <c r="B63" s="33"/>
+      <c r="C63" s="34"/>
+      <c r="D63" s="34"/>
+      <c r="E63" s="21"/>
+      <c r="F63" s="33"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A64" s="34"/>
-      <c r="B64" s="34"/>
-      <c r="C64" s="35"/>
-      <c r="D64" s="35"/>
-      <c r="E64" s="23"/>
-      <c r="F64" s="34"/>
+      <c r="A64" s="31"/>
+      <c r="B64" s="31"/>
+      <c r="C64" s="32"/>
+      <c r="D64" s="32"/>
+      <c r="E64" s="20"/>
+      <c r="F64" s="31"/>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A65" s="36"/>
-      <c r="B65" s="36"/>
-      <c r="C65" s="37"/>
-      <c r="D65" s="37"/>
-      <c r="E65" s="24"/>
-      <c r="F65" s="36"/>
+      <c r="A65" s="33"/>
+      <c r="B65" s="33"/>
+      <c r="C65" s="34"/>
+      <c r="D65" s="34"/>
+      <c r="E65" s="21"/>
+      <c r="F65" s="33"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A66" s="34"/>
-      <c r="B66" s="34"/>
-      <c r="C66" s="35"/>
-      <c r="D66" s="35"/>
-      <c r="E66" s="23"/>
-      <c r="F66" s="34"/>
+      <c r="A66" s="31"/>
+      <c r="B66" s="31"/>
+      <c r="C66" s="32"/>
+      <c r="D66" s="32"/>
+      <c r="E66" s="20"/>
+      <c r="F66" s="31"/>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A67" s="36"/>
-      <c r="B67" s="36"/>
-      <c r="C67" s="37"/>
-      <c r="D67" s="37"/>
-      <c r="E67" s="24"/>
-      <c r="F67" s="36"/>
+      <c r="A67" s="33"/>
+      <c r="B67" s="33"/>
+      <c r="C67" s="34"/>
+      <c r="D67" s="34"/>
+      <c r="E67" s="21"/>
+      <c r="F67" s="33"/>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A68" s="34"/>
-      <c r="B68" s="34"/>
-      <c r="C68" s="35"/>
-      <c r="D68" s="35"/>
-      <c r="E68" s="23"/>
-      <c r="F68" s="34"/>
+      <c r="A68" s="31"/>
+      <c r="B68" s="31"/>
+      <c r="C68" s="32"/>
+      <c r="D68" s="32"/>
+      <c r="E68" s="20"/>
+      <c r="F68" s="31"/>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A69" s="36"/>
-      <c r="B69" s="36"/>
-      <c r="C69" s="37"/>
-      <c r="D69" s="37"/>
-      <c r="E69" s="24"/>
-      <c r="F69" s="36"/>
+      <c r="A69" s="33"/>
+      <c r="B69" s="33"/>
+      <c r="C69" s="34"/>
+      <c r="D69" s="34"/>
+      <c r="E69" s="21"/>
+      <c r="F69" s="33"/>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A70" s="34"/>
-      <c r="B70" s="34"/>
-      <c r="C70" s="35"/>
-      <c r="D70" s="35"/>
-      <c r="E70" s="23"/>
-      <c r="F70" s="34"/>
+      <c r="A70" s="31"/>
+      <c r="B70" s="31"/>
+      <c r="C70" s="32"/>
+      <c r="D70" s="32"/>
+      <c r="E70" s="20"/>
+      <c r="F70" s="31"/>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A71" s="36"/>
-      <c r="B71" s="36"/>
-      <c r="C71" s="37"/>
-      <c r="D71" s="37"/>
-      <c r="E71" s="24"/>
-      <c r="F71" s="36"/>
+      <c r="A71" s="33"/>
+      <c r="B71" s="33"/>
+      <c r="C71" s="34"/>
+      <c r="D71" s="34"/>
+      <c r="E71" s="21"/>
+      <c r="F71" s="33"/>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A72" s="34"/>
-      <c r="B72" s="34"/>
-      <c r="C72" s="35"/>
-      <c r="D72" s="35"/>
-      <c r="E72" s="23"/>
-      <c r="F72" s="34"/>
+      <c r="A72" s="31"/>
+      <c r="B72" s="31"/>
+      <c r="C72" s="32"/>
+      <c r="D72" s="32"/>
+      <c r="E72" s="20"/>
+      <c r="F72" s="31"/>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A73" s="36"/>
-      <c r="B73" s="36"/>
-      <c r="C73" s="37"/>
-      <c r="D73" s="37"/>
-      <c r="E73" s="24"/>
-      <c r="F73" s="36"/>
+      <c r="A73" s="33"/>
+      <c r="B73" s="33"/>
+      <c r="C73" s="34"/>
+      <c r="D73" s="34"/>
+      <c r="E73" s="21"/>
+      <c r="F73" s="33"/>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A74" s="34"/>
-      <c r="B74" s="34"/>
-      <c r="C74" s="35"/>
-      <c r="D74" s="35"/>
-      <c r="E74" s="23"/>
-      <c r="F74" s="34"/>
+      <c r="A74" s="31"/>
+      <c r="B74" s="31"/>
+      <c r="C74" s="32"/>
+      <c r="D74" s="32"/>
+      <c r="E74" s="20"/>
+      <c r="F74" s="31"/>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A75" s="36"/>
-      <c r="B75" s="36"/>
-      <c r="C75" s="37"/>
-      <c r="D75" s="37"/>
-      <c r="E75" s="24"/>
-      <c r="F75" s="36"/>
+      <c r="A75" s="33"/>
+      <c r="B75" s="33"/>
+      <c r="C75" s="34"/>
+      <c r="D75" s="34"/>
+      <c r="E75" s="21"/>
+      <c r="F75" s="33"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A76" s="34"/>
-      <c r="B76" s="34"/>
-      <c r="C76" s="35"/>
-      <c r="D76" s="35"/>
-      <c r="E76" s="23"/>
-      <c r="F76" s="34"/>
+      <c r="A76" s="31"/>
+      <c r="B76" s="31"/>
+      <c r="C76" s="32"/>
+      <c r="D76" s="32"/>
+      <c r="E76" s="20"/>
+      <c r="F76" s="31"/>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A77" s="36"/>
-      <c r="B77" s="36"/>
-      <c r="C77" s="37"/>
-      <c r="D77" s="37"/>
-      <c r="E77" s="24"/>
-      <c r="F77" s="36"/>
+      <c r="A77" s="33"/>
+      <c r="B77" s="33"/>
+      <c r="C77" s="34"/>
+      <c r="D77" s="34"/>
+      <c r="E77" s="21"/>
+      <c r="F77" s="33"/>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A78" s="34"/>
-      <c r="B78" s="34"/>
-      <c r="C78" s="35"/>
-      <c r="D78" s="35"/>
-      <c r="E78" s="23"/>
-      <c r="F78" s="34"/>
+      <c r="A78" s="31"/>
+      <c r="B78" s="31"/>
+      <c r="C78" s="32"/>
+      <c r="D78" s="32"/>
+      <c r="E78" s="20"/>
+      <c r="F78" s="31"/>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A79" s="36"/>
-      <c r="B79" s="36"/>
-      <c r="C79" s="37"/>
-      <c r="D79" s="37"/>
-      <c r="E79" s="24"/>
-      <c r="F79" s="36"/>
+      <c r="A79" s="33"/>
+      <c r="B79" s="33"/>
+      <c r="C79" s="34"/>
+      <c r="D79" s="34"/>
+      <c r="E79" s="21"/>
+      <c r="F79" s="33"/>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A80" s="34"/>
-      <c r="B80" s="34"/>
-      <c r="C80" s="35"/>
-      <c r="D80" s="35"/>
-      <c r="E80" s="23"/>
-      <c r="F80" s="34"/>
+      <c r="A80" s="31"/>
+      <c r="B80" s="31"/>
+      <c r="C80" s="32"/>
+      <c r="D80" s="32"/>
+      <c r="E80" s="20"/>
+      <c r="F80" s="31"/>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A81" s="36"/>
-      <c r="B81" s="36"/>
-      <c r="C81" s="37"/>
-      <c r="D81" s="37"/>
-      <c r="E81" s="24"/>
-      <c r="F81" s="36"/>
+      <c r="A81" s="33"/>
+      <c r="B81" s="33"/>
+      <c r="C81" s="34"/>
+      <c r="D81" s="34"/>
+      <c r="E81" s="21"/>
+      <c r="F81" s="33"/>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A82" s="34"/>
-      <c r="B82" s="34"/>
-      <c r="C82" s="35"/>
-      <c r="D82" s="35"/>
-      <c r="E82" s="23"/>
-      <c r="F82" s="34"/>
+      <c r="A82" s="31"/>
+      <c r="B82" s="31"/>
+      <c r="C82" s="32"/>
+      <c r="D82" s="32"/>
+      <c r="E82" s="20"/>
+      <c r="F82" s="31"/>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A83" s="36"/>
-      <c r="B83" s="36"/>
-      <c r="C83" s="37"/>
-      <c r="D83" s="37"/>
-      <c r="E83" s="24"/>
-      <c r="F83" s="36"/>
+      <c r="A83" s="33"/>
+      <c r="B83" s="33"/>
+      <c r="C83" s="34"/>
+      <c r="D83" s="34"/>
+      <c r="E83" s="21"/>
+      <c r="F83" s="33"/>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A84" s="34"/>
-      <c r="B84" s="34"/>
-      <c r="C84" s="35"/>
-      <c r="D84" s="35"/>
-      <c r="E84" s="23"/>
-      <c r="F84" s="34"/>
+      <c r="A84" s="31"/>
+      <c r="B84" s="31"/>
+      <c r="C84" s="32"/>
+      <c r="D84" s="32"/>
+      <c r="E84" s="20"/>
+      <c r="F84" s="31"/>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A85" s="36"/>
-      <c r="B85" s="36"/>
-      <c r="C85" s="37"/>
-      <c r="D85" s="37"/>
-      <c r="E85" s="24"/>
-      <c r="F85" s="36"/>
+      <c r="A85" s="33"/>
+      <c r="B85" s="33"/>
+      <c r="C85" s="34"/>
+      <c r="D85" s="34"/>
+      <c r="E85" s="21"/>
+      <c r="F85" s="33"/>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A86" s="34"/>
-      <c r="B86" s="34"/>
-      <c r="C86" s="35"/>
-      <c r="D86" s="35"/>
-      <c r="E86" s="23"/>
-      <c r="F86" s="34"/>
+      <c r="A86" s="31"/>
+      <c r="B86" s="31"/>
+      <c r="C86" s="32"/>
+      <c r="D86" s="32"/>
+      <c r="E86" s="20"/>
+      <c r="F86" s="31"/>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A87" s="36"/>
-      <c r="B87" s="36"/>
-      <c r="C87" s="37"/>
-      <c r="D87" s="37"/>
-      <c r="E87" s="24"/>
-      <c r="F87" s="36"/>
+      <c r="A87" s="33"/>
+      <c r="B87" s="33"/>
+      <c r="C87" s="34"/>
+      <c r="D87" s="34"/>
+      <c r="E87" s="21"/>
+      <c r="F87" s="33"/>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A88" s="34"/>
-      <c r="B88" s="34"/>
-      <c r="C88" s="35"/>
-      <c r="D88" s="35"/>
-      <c r="E88" s="23"/>
-      <c r="F88" s="34"/>
+      <c r="A88" s="31"/>
+      <c r="B88" s="31"/>
+      <c r="C88" s="32"/>
+      <c r="D88" s="32"/>
+      <c r="E88" s="20"/>
+      <c r="F88" s="31"/>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A89" s="36"/>
-      <c r="B89" s="36"/>
-      <c r="C89" s="37"/>
-      <c r="D89" s="37"/>
-      <c r="E89" s="24"/>
-      <c r="F89" s="36"/>
+      <c r="A89" s="33"/>
+      <c r="B89" s="33"/>
+      <c r="C89" s="34"/>
+      <c r="D89" s="34"/>
+      <c r="E89" s="21"/>
+      <c r="F89" s="33"/>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A90" s="34"/>
-      <c r="B90" s="34"/>
-      <c r="C90" s="35"/>
-      <c r="D90" s="35"/>
-      <c r="E90" s="23"/>
-      <c r="F90" s="34"/>
+      <c r="A90" s="31"/>
+      <c r="B90" s="31"/>
+      <c r="C90" s="32"/>
+      <c r="D90" s="32"/>
+      <c r="E90" s="20"/>
+      <c r="F90" s="31"/>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A91" s="36"/>
-      <c r="B91" s="36"/>
-      <c r="C91" s="37"/>
-      <c r="D91" s="37"/>
-      <c r="E91" s="24"/>
-      <c r="F91" s="36"/>
+      <c r="A91" s="33"/>
+      <c r="B91" s="33"/>
+      <c r="C91" s="34"/>
+      <c r="D91" s="34"/>
+      <c r="E91" s="21"/>
+      <c r="F91" s="33"/>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A92" s="34"/>
-      <c r="B92" s="34"/>
-      <c r="C92" s="35"/>
-      <c r="D92" s="35"/>
-      <c r="E92" s="23"/>
-      <c r="F92" s="34"/>
+      <c r="A92" s="31"/>
+      <c r="B92" s="31"/>
+      <c r="C92" s="32"/>
+      <c r="D92" s="32"/>
+      <c r="E92" s="20"/>
+      <c r="F92" s="31"/>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A93" s="36"/>
-      <c r="B93" s="36"/>
-      <c r="C93" s="37"/>
-      <c r="D93" s="37"/>
-      <c r="E93" s="24"/>
-      <c r="F93" s="36"/>
+      <c r="A93" s="33"/>
+      <c r="B93" s="33"/>
+      <c r="C93" s="34"/>
+      <c r="D93" s="34"/>
+      <c r="E93" s="21"/>
+      <c r="F93" s="33"/>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A94" s="34"/>
-      <c r="B94" s="34"/>
-      <c r="C94" s="35"/>
-      <c r="D94" s="35"/>
-      <c r="E94" s="23"/>
-      <c r="F94" s="34"/>
+      <c r="A94" s="31"/>
+      <c r="B94" s="31"/>
+      <c r="C94" s="32"/>
+      <c r="D94" s="32"/>
+      <c r="E94" s="20"/>
+      <c r="F94" s="31"/>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A95" s="36"/>
-      <c r="B95" s="36"/>
-      <c r="C95" s="37"/>
-      <c r="D95" s="37"/>
-      <c r="E95" s="24"/>
-      <c r="F95" s="36"/>
+      <c r="A95" s="33"/>
+      <c r="B95" s="33"/>
+      <c r="C95" s="34"/>
+      <c r="D95" s="34"/>
+      <c r="E95" s="21"/>
+      <c r="F95" s="33"/>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A96" s="34"/>
-      <c r="B96" s="34"/>
-      <c r="C96" s="35"/>
-      <c r="D96" s="35"/>
-      <c r="E96" s="23"/>
-      <c r="F96" s="34"/>
+      <c r="A96" s="31"/>
+      <c r="B96" s="31"/>
+      <c r="C96" s="32"/>
+      <c r="D96" s="32"/>
+      <c r="E96" s="20"/>
+      <c r="F96" s="31"/>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A97" s="36"/>
-      <c r="B97" s="36"/>
-      <c r="C97" s="37"/>
-      <c r="D97" s="37"/>
-      <c r="E97" s="24"/>
-      <c r="F97" s="36"/>
+      <c r="A97" s="33"/>
+      <c r="B97" s="33"/>
+      <c r="C97" s="34"/>
+      <c r="D97" s="34"/>
+      <c r="E97" s="21"/>
+      <c r="F97" s="33"/>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A98" s="34"/>
-      <c r="B98" s="34"/>
-      <c r="C98" s="35"/>
-      <c r="D98" s="35"/>
-      <c r="E98" s="23"/>
-      <c r="F98" s="34"/>
+      <c r="A98" s="31"/>
+      <c r="B98" s="31"/>
+      <c r="C98" s="32"/>
+      <c r="D98" s="32"/>
+      <c r="E98" s="20"/>
+      <c r="F98" s="31"/>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A99" s="36"/>
-      <c r="B99" s="36"/>
-      <c r="C99" s="37"/>
-      <c r="D99" s="37"/>
-      <c r="E99" s="24"/>
-      <c r="F99" s="36"/>
+      <c r="A99" s="33"/>
+      <c r="B99" s="33"/>
+      <c r="C99" s="34"/>
+      <c r="D99" s="34"/>
+      <c r="E99" s="21"/>
+      <c r="F99" s="33"/>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A100" s="34"/>
-      <c r="B100" s="34"/>
-      <c r="C100" s="35"/>
-      <c r="D100" s="35"/>
-      <c r="E100" s="23"/>
-      <c r="F100" s="34"/>
+      <c r="A100" s="31"/>
+      <c r="B100" s="31"/>
+      <c r="C100" s="32"/>
+      <c r="D100" s="32"/>
+      <c r="E100" s="20"/>
+      <c r="F100" s="31"/>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A101" s="36"/>
-      <c r="B101" s="36"/>
-      <c r="C101" s="37"/>
-      <c r="D101" s="37"/>
-      <c r="E101" s="24"/>
-      <c r="F101" s="36"/>
+      <c r="A101" s="33"/>
+      <c r="B101" s="33"/>
+      <c r="C101" s="34"/>
+      <c r="D101" s="34"/>
+      <c r="E101" s="21"/>
+      <c r="F101" s="33"/>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A102" s="34"/>
-      <c r="B102" s="34"/>
-      <c r="C102" s="35"/>
-      <c r="D102" s="35"/>
-      <c r="E102" s="23"/>
-      <c r="F102" s="34"/>
+      <c r="A102" s="31"/>
+      <c r="B102" s="31"/>
+      <c r="C102" s="32"/>
+      <c r="D102" s="32"/>
+      <c r="E102" s="20"/>
+      <c r="F102" s="31"/>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A103" s="36"/>
-      <c r="B103" s="36"/>
-      <c r="C103" s="37"/>
-      <c r="D103" s="37"/>
-      <c r="E103" s="24"/>
-      <c r="F103" s="36"/>
+      <c r="A103" s="33"/>
+      <c r="B103" s="33"/>
+      <c r="C103" s="34"/>
+      <c r="D103" s="34"/>
+      <c r="E103" s="21"/>
+      <c r="F103" s="33"/>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A104" s="34"/>
-      <c r="B104" s="34"/>
-      <c r="C104" s="35"/>
-      <c r="D104" s="35"/>
-      <c r="E104" s="23"/>
-      <c r="F104" s="34"/>
+      <c r="A104" s="31"/>
+      <c r="B104" s="31"/>
+      <c r="C104" s="32"/>
+      <c r="D104" s="32"/>
+      <c r="E104" s="20"/>
+      <c r="F104" s="31"/>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A105" s="36"/>
-      <c r="B105" s="36"/>
-      <c r="C105" s="37"/>
-      <c r="D105" s="37"/>
-      <c r="E105" s="24"/>
-      <c r="F105" s="36"/>
+      <c r="A105" s="33"/>
+      <c r="B105" s="33"/>
+      <c r="C105" s="34"/>
+      <c r="D105" s="34"/>
+      <c r="E105" s="21"/>
+      <c r="F105" s="33"/>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A106" s="34"/>
-      <c r="B106" s="34"/>
-      <c r="C106" s="35"/>
-      <c r="D106" s="35"/>
-      <c r="E106" s="23"/>
-      <c r="F106" s="34"/>
+      <c r="A106" s="31"/>
+      <c r="B106" s="31"/>
+      <c r="C106" s="32"/>
+      <c r="D106" s="32"/>
+      <c r="E106" s="20"/>
+      <c r="F106" s="31"/>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A107" s="36"/>
-      <c r="B107" s="36"/>
-      <c r="C107" s="37"/>
-      <c r="D107" s="37"/>
-      <c r="E107" s="24"/>
-      <c r="F107" s="36"/>
+      <c r="A107" s="33"/>
+      <c r="B107" s="33"/>
+      <c r="C107" s="34"/>
+      <c r="D107" s="34"/>
+      <c r="E107" s="21"/>
+      <c r="F107" s="33"/>
     </row>
   </sheetData>
   <autoFilter ref="A7:F7"/>

--- a/public/downloads/invoice-template.xlsx
+++ b/public/downloads/invoice-template.xlsx
@@ -823,33 +823,28 @@
     <tabColor rgb="FF4A4A48"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:A26"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="40" customWidth="1"/>
-    <col min="2" max="3" width="30" customWidth="1"/>
+    <col min="1" max="1" width="104" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25.5" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" ht="25.5" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-    </row>
-    <row r="2" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
     </row>
     <row r="4" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" ht="33.75" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" ht="16.75" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>3</v>
       </c>
@@ -859,7 +854,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" ht="33.75" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" ht="29.5" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>5</v>
       </c>
@@ -869,22 +864,22 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" ht="33.75" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" ht="16.75" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="13" ht="33.75" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" ht="16.75" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="15" ht="33.75" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" ht="16.75" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="17" ht="33.75" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" ht="16.75" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>10</v>
       </c>
@@ -894,7 +889,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="20" ht="48" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" ht="55" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
         <v>12</v>
       </c>
@@ -904,7 +899,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="23" ht="33.75" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" ht="29.5" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
         <v>14</v>
       </c>
@@ -914,7 +909,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26" ht="48" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" ht="42.25" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
         <v>16</v>
       </c>
